--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
@@ -575,46 +575,46 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.92761431137136</v>
+        <v>15.87670547636138</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.055088661316802</v>
+        <v>9.026412511902322</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.662130073812691</v>
+        <v>8.635376224997088</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.527617966124716</v>
+        <v>3.516747231005731</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.989512117079066</v>
+        <v>2.980334126148861</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.25129078478269</v>
+        <v>-7.227617647260985</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.338122599803803</v>
+        <v>-7.313849106744186</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.08038352624009</v>
+        <v>-13.03744121391622</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.14481715790193</v>
+        <v>-13.10166279820712</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.725084228230088</v>
+        <v>-8.696402892895975</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-14.20872568911469</v>
+        <v>-14.16246317293619</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-19.455274940463</v>
+        <v>-19.39221186380534</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.045238024488675</v>
+        <v>-4.03164953381706</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.07573044580792</v>
+        <v>-9.046131364793027</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.634262339589064</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.038585513941122</v>
+        <v>3.028961558579134</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.361283902462304</v>
+        <v>8.335142949367786</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.775210991815257</v>
+        <v>2.766625115286004</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.956893783836364</v>
+        <v>7.931544924819399</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.11727545698193</v>
+        <v>11.08192448622148</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.173577641913113</v>
+        <v>8.148064521029077</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.56946913410484</v>
+        <v>10.53658411051851</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.648043862313436</v>
+        <v>7.624603575430932</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.5251847667768</v>
+        <v>12.48559952536554</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.32289562386887</v>
+        <v>12.28406547076528</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.964569431052254</v>
+        <v>-1.957165838857257</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4793646985049378</v>
+        <v>0.4785182843768681</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.136416155221141</v>
+        <v>-2.128838131710317</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.6329732039309</v>
+        <v>-10.59852182698567</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.269134664306584</v>
+        <v>-5.251818229367231</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10.31911842476784</v>
+        <v>-10.28477049669737</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8819912298056707</v>
+        <v>-0.8788026952540093</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.9067734658913551</v>
+        <v>0.9039501916847072</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.20475984776516</v>
+        <v>1.201085673590143</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.538195307645296</v>
+        <v>-3.525963383336013</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.677632263794557</v>
+        <v>-1.671168559341496</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.730101086800303</v>
+        <v>-8.700517625388969</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.253211332736761</v>
+        <v>-7.228985596890269</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.12330839801175</v>
+        <v>-12.08307000041183</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.428294110131645</v>
+        <v>-7.402903604848269</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.186154082441881</v>
+        <v>-3.175047287864743</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.269720058905015</v>
+        <v>-5.251761719750178</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.434614790797319</v>
+        <v>-5.416534973632324</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.797128535763413</v>
+        <v>0.7947926356613664</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-9.406787823174213</v>
+        <v>-9.37463622909452</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.429622491034031</v>
+        <v>-1.424546188380098</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.006127621518004389</v>
+        <v>-0.005998649830019076</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-15.41461781209339</v>
+        <v>-15.36340482667576</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-17.46748516832506</v>
+        <v>-17.4088841424707</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-14.01158589027941</v>
+        <v>-13.9641682455309</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-14.07657726021251</v>
+        <v>-14.02860065996408</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-16.89722103323702</v>
+        <v>-16.84051454795735</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-9.243945098465446</v>
+        <v>-9.212268867157633</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-9.21218684023799</v>
+        <v>-9.180288112817763</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-11.60243073786576</v>
+        <v>-11.5632181836931</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.387738709697295</v>
+        <v>-9.355728888013729</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>73</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.301082227734298</v>
+        <v>2.293670169371026</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.05077032275635</v>
+        <v>-2.043582491060505</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.076008704834159</v>
+        <v>-1.07090230932063</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.796055892424427</v>
+        <v>1.790423261333494</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.257604465531124</v>
+        <v>1.253478180634573</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.927086397369507</v>
+        <v>2.918125220348138</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09858990539394341</v>
+        <v>0.09986854370534104</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.375109159747801</v>
+        <v>2.36881997335842</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.059667033447191</v>
+        <v>5.044687430068961</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.955186872686738</v>
+        <v>6.933322007538848</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.125042029736349</v>
+        <v>8.099194543133606</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.08145409668942705</v>
+        <v>-0.07930493718997411</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.245560185606152</v>
+        <v>2.239358810484816</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.626912959801771</v>
+        <v>-1.62003186947878</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.480920654149287</v>
+        <v>6.5436516522795</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.84733797412583</v>
+        <v>13.98143743192676</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.911139700500293</v>
+        <v>1.925242642255121</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.939312961829835</v>
+        <v>-7.008023601978358</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.480079602192966</v>
+        <v>-7.553262076129258</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.900753869059756</v>
+        <v>-5.960536639123028</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.277574472221879</v>
+        <v>-5.333878018451593</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.457066093075078</v>
+        <v>-4.505242671333704</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.518072420272624</v>
+        <v>-4.567405652195831</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-7.931954633789481</v>
+        <v>-8.012825851295105</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.996670519355874</v>
+        <v>-3.028988998643861</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8954656092903974</v>
+        <v>0.8986625810973479</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.094075460914894</v>
+        <v>-2.118158467519294</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7256437740633785</v>
+        <v>0.7283047254325368</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.920622786229167</v>
+        <v>-4.95350601826037</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.505067993466675</v>
+        <v>-7.554876085646349</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.482133614836911</v>
+        <v>-3.508720077054804</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.355970963831503</v>
+        <v>-3.380348870111362</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.89123413416106</v>
+        <v>-3.918742967713584</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2918113389150179</v>
+        <v>0.2914550235398252</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.181981709053971</v>
+        <v>1.185901178181119</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.579604137023935</v>
+        <v>5.613542195964349</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.603562009955837</v>
+        <v>2.616910230419492</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.705139864055383</v>
+        <v>3.726768473016442</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.393734888023246</v>
+        <v>7.441307366775234</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>9.377619064269155</v>
+        <v>9.437411762755218</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.09412412924155</v>
+        <v>4.119031157877352</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.395764638726241</v>
+        <v>2.408976994340108</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-12.14256112722752</v>
+        <v>-12.2160098156666</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.861055872203302</v>
+        <v>-5.896592273177959</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.378737427908291</v>
+        <v>-5.41439882046906</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.005330242866911</v>
+        <v>-7.049524116089266</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-11.05794737711539</v>
+        <v>-11.12616188318678</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.103462347764882</v>
+        <v>-1.112183118151385</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.57945919238044</v>
+        <v>-5.616569955866204</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.413540724183186</v>
+        <v>-3.436700996395992</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6.111989560600804</v>
+        <v>-6.152259030723464</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.69184752150823</v>
+        <v>-1.70459582110022</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.400274142701441</v>
+        <v>-1.409800485796254</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.365700636974331</v>
+        <v>-1.37581076380237</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.301429623048385</v>
+        <v>-5.335248324532564</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.813665090088215</v>
+        <v>-6.857030293530798</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.84243160880073</v>
+        <v>-4.864158786084104</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.113289983931033</v>
+        <v>-5.135222962980556</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.494409142885445</v>
+        <v>-3.51176791803276</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.394431307003778</v>
+        <v>-7.427118308569291</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.24879650764192</v>
+        <v>-5.272957313811801</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.296297987038109</v>
+        <v>-6.323733974375692</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.037735468571981</v>
+        <v>-5.061621208006912</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.17910594480982</v>
+        <v>-6.206743722362575</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.897960526726472</v>
+        <v>-4.921310682854006</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.405847277529602</v>
+        <v>-4.425948587007532</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.628045777714405</v>
+        <v>-6.65619180134285</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.905042354314425</v>
+        <v>-3.922571236576111</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.982177539434183</v>
+        <v>-2.996455917796318</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.367053357232528</v>
+        <v>-4.387525390397727</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>185</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.142086968858628</v>
+        <v>-1.136991234553619</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5918264596241727</v>
+        <v>-0.5888740999520081</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.1497907351213</v>
+        <v>-3.138437714801718</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.265972960868304</v>
+        <v>-6.245931932708835</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7675053014055493</v>
+        <v>0.7678702575095713</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.524330245495662</v>
+        <v>0.5247759820147593</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.52147298070323</v>
+        <v>1.520129131575032</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.136762287634767</v>
+        <v>2.133182283994572</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.715136896357194</v>
+        <v>-1.70744696168488</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.025523717997125</v>
+        <v>-2.01790097479617</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.230340848484182</v>
+        <v>-2.222636068779899</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.654900893633332</v>
+        <v>-1.648740000477403</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.161388596222281</v>
+        <v>-3.150760236187502</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.911502992538693</v>
+        <v>-2.901038903910973</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08702120791051016</v>
+        <v>-0.08941767772593323</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.115090214733307</v>
+        <v>3.12215743521211</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.04520878958030039</v>
+        <v>0.04217597033588305</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.245287390592132</v>
+        <v>1.245044990571522</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8991342378028548</v>
+        <v>-0.9040646781665842</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.278933376387883</v>
+        <v>-3.289783653036089</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.364198178028055</v>
+        <v>-3.376151311327831</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.155008841973313</v>
+        <v>-1.160291958784029</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.289233783123031</v>
+        <v>-2.298767467214688</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.835287904746984</v>
+        <v>-2.845395711328578</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.504119711350597</v>
+        <v>-2.512848457785012</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.934932271500514</v>
+        <v>-1.942078876343103</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.818223623737993</v>
+        <v>-1.825564072281537</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5760079311268171</v>
+        <v>0.5746948944032368</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>226</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.931340440851969</v>
+        <v>1.928251102578244</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.418195272529942</v>
+        <v>3.409528777339396</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.678693064666</v>
+        <v>5.666032632711762</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.367747763926509</v>
+        <v>5.356299776912216</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.944628935268788</v>
+        <v>3.936308574254191</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.357433424917488</v>
+        <v>3.35055654586585</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.942768053529335</v>
+        <v>1.940887226072299</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7406558642440331</v>
+        <v>-0.7359987046723759</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8034750302465241</v>
+        <v>-0.7971683575099817</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.449234762110017</v>
+        <v>1.448221641991786</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.085787577414699</v>
+        <v>-0.08302018168152614</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9387135218272533</v>
+        <v>-0.9336519260037335</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.692564520799593</v>
+        <v>-2.681972864745141</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.442279386779958</v>
+        <v>-2.43225153246874</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.348400152271047</v>
+        <v>-1.359609445088338</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.343011107895748</v>
+        <v>-3.361468827626503</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.501983314930669</v>
+        <v>-4.530563522679628</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.991871308613192</v>
+        <v>-4.018533916604873</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.296871146626017</v>
+        <v>-5.329234590170543</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.943060099477634</v>
+        <v>-1.957362741675183</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.17552202882564</v>
+        <v>-3.198965647926428</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.6449614713855</v>
+        <v>-3.669849334906182</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.402044293328913</v>
+        <v>-5.43929080075587</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.574574334722172</v>
+        <v>-3.599271003095858</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.691270641008941</v>
+        <v>-5.726715202040673</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.129209638011943</v>
+        <v>-4.156439695407258</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.413554529022477</v>
+        <v>-2.433504518931663</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2520726121057777</v>
+        <v>-0.2607062635784487</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7861212470392402</v>
+        <v>-0.7909802263679779</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.50518094180434</v>
+        <v>1.508013571821515</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.573782739074133</v>
+        <v>2.576977700657835</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.704543670865007</v>
+        <v>2.707787765185131</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>6.834691385472439</v>
+        <v>6.849686596955998</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.620411362048799</v>
+        <v>7.638644648954383</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.096220078548662</v>
+        <v>5.105656655296109</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>6.585987425657173</v>
+        <v>6.600009282823194</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.573183887727119</v>
+        <v>4.579429949214706</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.700582920641416</v>
+        <v>4.709312151757103</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.496827991442927</v>
+        <v>4.504692774428776</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.043102508334506</v>
+        <v>4.050098508302831</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.135732349064867</v>
+        <v>3.139647818926562</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.384264090984978</v>
+        <v>3.38936915120285</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.121053382971482</v>
+        <v>-3.130810721510429</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.735057126481664</v>
+        <v>-4.746829985806585</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.711943886619828</v>
+        <v>-4.72579067021492</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.092284808477885</v>
+        <v>-3.102667047540123</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.793330752327925</v>
+        <v>-2.801887389622252</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.013047065673703</v>
+        <v>-5.025579338722345</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.187642092647778</v>
+        <v>1.187196972958809</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1172253370605958</v>
+        <v>-0.1199436312985469</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.919872714316881</v>
+        <v>1.919425961427081</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1872706733359166</v>
+        <v>-0.1906048952712425</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.02792594676561322</v>
+        <v>0.02477239695485878</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.615498405950369</v>
+        <v>-1.622170399260192</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.195679915318138</v>
+        <v>-1.202088875751407</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.366239672207769</v>
+        <v>-1.37253561070191</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.501387419296833</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.479740857001723</v>
+        <v>-2.486428557390987</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.298098313937288</v>
+        <v>-4.310303112668954</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.668522871760715</v>
+        <v>-1.675515946596967</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.921399223726425</v>
+        <v>-2.92968505038823</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.556067742225984</v>
+        <v>-1.561139837482671</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.639508767177624</v>
+        <v>-1.645406216020561</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3950340769350973</v>
+        <v>0.3934734817327765</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6940415889374876</v>
+        <v>0.6912461394670757</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.631938863114328</v>
+        <v>1.632332713516462</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3554086111084942</v>
+        <v>0.3530810440705849</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.820105701289698</v>
+        <v>1.820496990276354</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.401229494729485</v>
+        <v>1.400242379331452</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.650031890749283</v>
+        <v>1.649963711607661</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>275</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.675256502028155</v>
+        <v>-2.665775462475999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.832284660446994</v>
+        <v>-2.823922830324655</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.408971548861736</v>
+        <v>-1.400531036320601</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1878093253450999</v>
+        <v>-0.1826358603575287</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3646785504917816</v>
+        <v>0.367851562959487</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06613533985101583</v>
+        <v>-0.06318603749387819</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5150565976561268</v>
+        <v>-0.5104537646095295</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.9291646573432</v>
+        <v>1.927995456831667</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.687278923193702</v>
+        <v>3.684711221905744</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.01676997057254</v>
+        <v>1.017505193401625</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.631836140265726</v>
+        <v>2.630114849351394</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.302816701174791</v>
+        <v>2.301435406698481</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.516633455698909</v>
+        <v>1.517544432117333</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.674394896360063</v>
+        <v>0.6763566734844488</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.320515168162117</v>
+        <v>3.32203116713444</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5461508575234362</v>
+        <v>0.5340544490562493</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1512821509268463</v>
+        <v>0.1260576124695376</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.769907376557569</v>
+        <v>3.775560789392074</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.006679959935056</v>
+        <v>4.0186921462372</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3486462960510011</v>
+        <v>-0.3632830562519729</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.89349996611211</v>
+        <v>1.890702640513155</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8696848417166265</v>
+        <v>0.8672461541944472</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.03589522056521588</v>
+        <v>0.02122089752240441</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4257332288668607</v>
+        <v>-0.4390343616033974</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1463067400916813</v>
+        <v>0.1362038572490789</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.147545566280385</v>
+        <v>-1.165894138755988</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3969051518029048</v>
+        <v>-0.4142737497009321</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2375595736286016</v>
+        <v>0.2260725825754406</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>8.237155287096009</v>
+        <v>8.260893993755481</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.342476651300707</v>
+        <v>4.350433190848911</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>8.970438994932323</v>
+        <v>8.991171574522888</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.274208109275037</v>
+        <v>7.294703107855426</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.996060866805607</v>
+        <v>4.005404103679076</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.922529091081863</v>
+        <v>5.939851931076547</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.295826790745039</v>
+        <v>6.313833810134497</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.282443571791113</v>
+        <v>6.305366007683268</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.77081693361221</v>
+        <v>5.785650525170695</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.464775950202672</v>
+        <v>4.476809743812439</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.261080435162164</v>
+        <v>4.272056419494959</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.035542222997123</v>
+        <v>7.058733154821994</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.336766429421488</v>
+        <v>4.344900562225718</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.866771959790185</v>
+        <v>6.888199876153436</v>
       </c>
     </row>
     <row r="25">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.01059</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.0323095954349526</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.009757</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4046</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.04209562496484409</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.008926</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4011~4024</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4011</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.08290154088592061</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.008095</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3968~3981</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3968</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.03105301362574409</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.007265</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3917~3930</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3917</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.1019815271182622</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.006434</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3844~3857</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3844</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.06035996861554338</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.005603</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3767~3779</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3767</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.07216285050899529</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.004772</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3665~3676</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3665</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.06368899208599288</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.003942</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3552~3562</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3552</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.4543438246524545</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.003111</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3404~3413</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3404</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.6855830685975235</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.00228</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3219~3228</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3219</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.7903287182039023</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.00145</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3033~3041</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3033</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.84427953575846</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.0006189</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2807~2815</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2807</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7570057295235912</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.0002119</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2547~2553</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2547</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.9730716680391467</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.001043</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2343~2348</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2343</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.126663894440789</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.001873</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2105~2109</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2105</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.608031570733601</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.002704</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1826~1829</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1826</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.235921985968268</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.003535</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1551~1554</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1551</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.105017278245626</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.004365</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1295~1296</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1295</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.062117235345582</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.005196</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1077~1077</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1077</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.009811447663743</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.006027</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>868~868</t>
-        </is>
+      <c r="B26" t="n">
+        <v>868</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.654027117578046</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.006858</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>696~696</t>
-        </is>
+      <c r="B27" t="n">
+        <v>696</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.816906507376231</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.007688</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>565~565</t>
-        </is>
+      <c r="B28" t="n">
+        <v>565</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.081782918728081</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.008519</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>451~451</t>
-        </is>
+      <c r="B29" t="n">
+        <v>451</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>4.491040615488473</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.00935</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>345~345</t>
-        </is>
+      <c r="B30" t="n">
+        <v>345</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.158735592833501</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01018</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>251~251</t>
-        </is>
+      <c r="B31" t="n">
+        <v>251</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3.283454110068902</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01101</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B32" t="n">
+        <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.82235115347423</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.01184</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>156~156</t>
-        </is>
+      <c r="B33" t="n">
+        <v>156</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.275792449020798</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.01267</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B34" t="n">
+        <v>116</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.0135</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.01059</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.009757</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B7" t="n">
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.846367505032738</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.008926</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>138~138</t>
-        </is>
+      <c r="B8" t="n">
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.303663129065392</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.008095</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>181~181</t>
-        </is>
+      <c r="B9" t="n">
+        <v>181</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.007250474906108195</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.007265</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>232~232</t>
-        </is>
+      <c r="B10" t="n">
+        <v>232</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.20033487193411</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.006434</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>305~305</t>
-        </is>
+      <c r="B11" t="n">
+        <v>305</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3622907792263703</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.005603</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>382~383</t>
-        </is>
+      <c r="B12" t="n">
+        <v>382</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.031365857335715</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.004772</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>484~486</t>
-        </is>
+      <c r="B13" t="n">
+        <v>484</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2300638346132757</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.003942</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>597~600</t>
-        </is>
+      <c r="B14" t="n">
+        <v>597</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.003111</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>745~749</t>
-        </is>
+      <c r="B15" t="n">
+        <v>745</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-2.960728039836141</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.00228</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>930~934</t>
-        </is>
+      <c r="B16" t="n">
+        <v>930</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-2.60050470136629</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.00145</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1116~1121</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1116</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-2.181217089166267</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.0006189</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1342~1347</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1342</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.491211148717767</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.0002119</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1602~1609</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1602</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.467956654579154</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.001043</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1806~1814</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1806</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.390902487795422</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.001873</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2044~2053</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2044</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.592318008471054</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.002704</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2323~2333</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2323</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.700467895863639</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.003535</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2598~2608</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2598</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.803254271130221</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.004365</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2854~2866</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2854</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.342007754962239</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.005196</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3072~3085</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3072</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.6619958566767465</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.006027</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3281~3294</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3281</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.3987206517218169</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.006858</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3453~3466</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3453</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.3295606514275207</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.007688</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3584~3597</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3584</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.4500688456478343</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.008519</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3698~3711</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3698</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.5128400987063344</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.00935</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3804~3817</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3804</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.2534592790782</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01018</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3898~3911</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3898</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1794521274204115</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01101</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3959~3972</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3959</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1520485921132959</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.01184</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3993~4006</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3993</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.09703292829784971</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.01267</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4033~4046</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4033</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.02757008315137455</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.0135</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4065</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.01673405341252732</v>

--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,1034 +575,1034 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.87670547636138</v>
+        <v>15.88919907301814</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.026412511902322</v>
+        <v>9.039289545216015</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.635376224997088</v>
+        <v>8.64835249410973</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.516747231005731</v>
+        <v>3.529695474970765</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.980334126148861</v>
+        <v>2.993416530898344</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.227617647260985</v>
+        <v>-7.214604857179907</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.313849106744186</v>
+        <v>-7.30080936589443</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.03744121391622</v>
+        <v>-13.02428526824142</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.10166279820712</v>
+        <v>-13.08848499404926</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.696402892895975</v>
+        <v>-8.683013603411254</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-14.16246317293619</v>
+        <v>-14.149018803397</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-19.39221186380534</v>
+        <v>-19.37876882908612</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.03164953381706</v>
+        <v>-4.018097199553715</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.046131364793027</v>
+        <v>-9.056561000488777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.009341</t>
+          <t>X ≈ -0.009337</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.634262339589064</v>
+        <v>4.646746668728049</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.028961558579134</v>
+        <v>3.041833781613164</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.335142949367786</v>
+        <v>8.348118675310978</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.766625115286004</v>
+        <v>2.779572507414123</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.931544924819399</v>
+        <v>7.944629732365392</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.08192448622148</v>
+        <v>11.09494590734505</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.148064521029077</v>
+        <v>8.161110575999224</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.53658411051851</v>
+        <v>10.5497484294582</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.624603575430932</v>
+        <v>7.637787474403623</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.48559952536554</v>
+        <v>12.4989938322415</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.28406547076528</v>
+        <v>12.29751455732915</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.957165838857257</v>
+        <v>-1.943720795349947</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4785182843768681</v>
+        <v>0.4920708453849727</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.128838131710317</v>
+        <v>-2.139267767408469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.008511</t>
+          <t>X ≈ -0.008507</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.59852182698567</v>
+        <v>-10.58605069945074</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.251818229367231</v>
+        <v>-5.238952989452137</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10.28477049669737</v>
+        <v>-10.27180824626711</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8788026952540093</v>
+        <v>-0.8658582017874252</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.9039501916847072</v>
+        <v>0.9170305692686824</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.201085673590143</v>
+        <v>1.21410177198797</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.525963383336013</v>
+        <v>-3.512922836363316</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.671168559341496</v>
+        <v>-1.658009136702063</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.700517625388969</v>
+        <v>-8.687339149486512</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.228985596890269</v>
+        <v>-7.215596444349011</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.08307000041183</v>
+        <v>-12.0696256688201</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.402903604848269</v>
+        <v>-7.389459400510226</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.175047287864743</v>
+        <v>-3.161495026939008</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.251761719750178</v>
+        <v>-5.26219135544833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.00768</t>
+          <t>X ≈ -0.007676</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.416534973632324</v>
+        <v>-5.404060904781751</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7947926356613664</v>
+        <v>0.8076614254641683</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-9.37463622909452</v>
+        <v>-9.361674579419571</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.424546188380098</v>
+        <v>-1.411602893774145</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.005998649830019076</v>
+        <v>0.007080478967502302</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-15.36340482667576</v>
+        <v>-15.35039797323735</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-17.4088841424707</v>
+        <v>-17.39585057243254</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-13.9641682455309</v>
+        <v>-13.95101415698013</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-14.02860065996408</v>
+        <v>-14.01542447287204</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-16.84051454795735</v>
+        <v>-16.82712832650589</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-9.212268867157633</v>
+        <v>-9.198824342388335</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-9.180288112817763</v>
+        <v>-9.166844357765164</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-11.5632181836931</v>
+        <v>-11.5496665652316</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.355728888013729</v>
+        <v>-9.366158523711881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006849</t>
+          <t>X ≈ -0.006846</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>73</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.293670169371026</v>
+        <v>2.306149295895132</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.043582491060505</v>
+        <v>-2.030717299282422</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.07090230932063</v>
+        <v>-1.057936187482603</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.790423261333494</v>
+        <v>1.803367539732058</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.253478180634573</v>
+        <v>1.266557054677577</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.918125220348138</v>
+        <v>2.931140524587839</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09986854370534104</v>
+        <v>0.1129090745566117</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.36881997335842</v>
+        <v>2.38197963178586</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.044687430068961</v>
+        <v>5.057869180145474</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.933322007538848</v>
+        <v>6.946713900964205</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.099194543133606</v>
+        <v>8.112642106196148</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.07930493718997411</v>
+        <v>-0.065860267479529</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.239358810484816</v>
+        <v>2.252911194500591</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.62003186947878</v>
+        <v>-1.630461505176307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.006018</t>
+          <t>X ≈ -0.006015</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>77</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.5436516522795</v>
+        <v>6.556312509027052</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.98143743192676</v>
+        <v>13.99449908467915</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.925242642255121</v>
+        <v>1.938397706860172</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.008023601978358</v>
+        <v>-6.994899574546217</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.553262076129258</v>
+        <v>-7.540001046967987</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.960536639123028</v>
+        <v>-5.947338707126598</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.333878018451593</v>
+        <v>-6.037683725496031</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.505242671333704</v>
+        <v>-4.49208673201364</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.567405652195831</v>
+        <v>-4.554227898197766</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-8.012825851295105</v>
+        <v>-7.999438620607549</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.028988998643861</v>
+        <v>-3.015544109791726</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8986625810973479</v>
+        <v>0.9121070818958188</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.118158467519294</v>
+        <v>-2.104606531132326</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897337949</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005188</t>
+          <t>X ≈ -0.005184</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.95350601826037</v>
+        <v>-5.400920772802777</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.554876085646349</v>
+        <v>-7.992384865838709</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.508720077054804</v>
+        <v>-4.522494668323361</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.380348870111362</v>
+        <v>-3.861147943213972</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.918742967713584</v>
+        <v>-4.399541153557259</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2914550235398252</v>
+        <v>-0.2275424547320881</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.185901178181119</v>
+        <v>0.6574655650660191</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.613542195964349</v>
+        <v>5.037524640187861</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.616910230419492</v>
+        <v>2.069270042963083</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.726768473016442</v>
+        <v>3.160169648333088</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.441307366775234</v>
+        <v>6.83656431275201</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>9.437411762755218</v>
+        <v>8.813472834506264</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.119031157877352</v>
+        <v>3.542605080749617</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>1.827445131343261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.004357</t>
+          <t>X ≈ -0.004354</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-12.2160098156666</v>
+        <v>-11.84519445449187</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.896592273177959</v>
+        <v>-5.454476001520433</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-5.41439882046906</v>
+        <v>-4.966025967775309</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.049524116089266</v>
+        <v>-6.615146145076693</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-11.12616188318678</v>
+        <v>-10.7231166085927</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.112183118151385</v>
+        <v>-0.6223036481673887</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.616569955866204</v>
+        <v>-5.167869494500714</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.436700996395992</v>
+        <v>-2.962381425291859</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6.152259030723464</v>
+        <v>-5.701486451588941</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.70459582110022</v>
+        <v>-1.20617882125309</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.409800485796254</v>
+        <v>-1.411015988359836</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.37581076380237</v>
+        <v>-0.8727481268870676</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.335248324532564</v>
+        <v>-4.863541016523499</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.857030293530798</v>
+        <v>-6.424982053122555</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.003527</t>
+          <t>X ≈ -0.003523</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.864158786084104</v>
+        <v>-4.440215585810861</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.135222962980556</v>
+        <v>-5.393008069547733</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.51176791803276</v>
+        <v>-3.818232163923135</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.427118308569291</v>
+        <v>-7.626836945811654</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.272957313811801</v>
+        <v>-5.54011516109523</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.323733974375692</v>
+        <v>-6.55898914916083</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.061621208006912</v>
+        <v>-4.674228729167218</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.206743722362575</v>
+        <v>-5.797896249320956</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.921310682854006</v>
+        <v>-4.546152067964194</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.425948587007532</v>
+        <v>-4.739839344164956</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.65619180134285</v>
+        <v>-6.918625898663485</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.922571236576111</v>
+        <v>-4.25416582554093</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.996455917796318</v>
+        <v>-3.360110155801443</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.387525390397727</v>
+        <v>-4.451297842596595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.002695</t>
+          <t>X ≈ -0.002693</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.136991234553619</v>
+        <v>-1.109264683589615</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5888740999520081</v>
+        <v>0.007587250647901556</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.138437714801718</v>
+        <v>-2.565554030281696</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.245931932708835</v>
+        <v>-5.706250472792142</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.7678702575095713</v>
+        <v>1.388185612579655</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5247759820147593</v>
+        <v>1.139322564181732</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.520129131575032</v>
+        <v>1.601011612199237</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.133182283994572</v>
+        <v>2.225553607132881</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.70744696168488</v>
+        <v>-1.655074292342</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.01790097479617</v>
+        <v>-1.413440696847637</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.222636068779899</v>
+        <v>-1.618777626841023</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.648740000477403</v>
+        <v>-1.038309047875927</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.150760236187502</v>
+        <v>-2.551356468757753</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.901038903910973</v>
+        <v>-2.326621397385047</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.001865</t>
+          <t>X ≈ -0.001862</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08941767772593323</v>
+        <v>-0.3559244008626834</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.12215743521211</v>
+        <v>2.829039331761557</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.04217597033588305</v>
+        <v>-0.2357565356466935</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.245044990571522</v>
+        <v>0.9614290364580427</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9040646781665842</v>
+        <v>-1.17845659466311</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.289783653036089</v>
+        <v>-3.54927369000027</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.376151311327831</v>
+        <v>-3.637067530656466</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.160291958784029</v>
+        <v>-1.434736994436179</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.298767467214688</v>
+        <v>-2.032775871839021</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.845395711328578</v>
+        <v>-2.886164078006537</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.512848457785012</v>
+        <v>-2.25230729854075</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.942078876343103</v>
+        <v>-1.683563372571825</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.825564072281537</v>
+        <v>-2.104287935147255</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5746948944032368</v>
+        <v>0.2595099254868742</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.001034</t>
+          <t>X ≈ -0.001032</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.928251102578244</v>
+        <v>1.979720090129511</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.409528777339396</v>
+        <v>3.488286731878645</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.666032632711762</v>
+        <v>5.769689095022322</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.356299776912216</v>
+        <v>5.454514304443514</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.936308574254191</v>
+        <v>4.027195970370336</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.35055654586585</v>
+        <v>3.433701397759492</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.940887226072299</v>
+        <v>2.013135187787555</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.7359987046723759</v>
+        <v>-0.6828062445323937</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7971683575099817</v>
+        <v>-1.1897197547639</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.448221641991786</v>
+        <v>1.082609945152612</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.08302018168152614</v>
+        <v>-0.4604233597789857</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.9336519260037335</v>
+        <v>-1.318337063577466</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.681972864745141</v>
+        <v>-2.631554705995299</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.43225153246874</v>
+        <v>-2.407124910265615</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.0002035</t>
+          <t>X ≈ -0.0002012</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>260</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.359609445088338</v>
+        <v>-1.346165176088277</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.361468827626503</v>
+        <v>-3.347091271011415</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.530563522679628</v>
+        <v>-4.517556391262026</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.018533916604873</v>
+        <v>-4.003469419846439</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.329234590170543</v>
+        <v>-5.313607214875525</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.957362741675183</v>
+        <v>-1.943132652989242</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.198965647926428</v>
+        <v>-3.185899393625952</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.669849334906182</v>
+        <v>-3.654686698211513</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.43929080075587</v>
+        <v>-5.64438711416161</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.599271003095858</v>
+        <v>-3.585865875443027</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.726715202040673</v>
+        <v>-5.713257908330455</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.156439695407258</v>
+        <v>-4.140899112220872</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.433504518931663</v>
+        <v>-2.642937734030852</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2607062635784487</v>
+        <v>-0.2711358992766009</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0006275</t>
+          <t>X ≈ 0.0006295</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>204</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7909802263679779</v>
+        <v>-0.7776580714952033</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.508013571821515</v>
+        <v>1.520544451836543</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.576977700657835</v>
+        <v>2.589984832075437</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.707787765185131</v>
+        <v>2.720334948351613</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>6.849686596955998</v>
+        <v>6.587182573574992</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.638644648954383</v>
+        <v>7.648837997336784</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.105656655296109</v>
+        <v>5.118722909596585</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>6.600009282823194</v>
+        <v>6.611000484169274</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.579429949214706</v>
+        <v>4.592628688169469</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.709312151757103</v>
+        <v>4.722717279409935</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.504692774428776</v>
+        <v>4.518150068138993</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.050098508302831</v>
+        <v>4.062457553214472</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.139647818926562</v>
+        <v>3.153203865278165</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.38936915120285</v>
+        <v>3.378939515504698</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.001458</t>
+          <t>X ≈ 0.00146</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>238</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.130810721510429</v>
+        <v>-3.11622907968858</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.746829985806585</v>
+        <v>-4.731431150237938</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.72579067021492</v>
+        <v>-4.712783538797318</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.102667047540123</v>
+        <v>-3.323729948257125</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.801887389622252</v>
+        <v>-2.788776585247312</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.025579338722345</v>
+        <v>-5.009975779803185</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.187196972958809</v>
+        <v>1.200263227259285</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1199436312985469</v>
+        <v>-0.1062224547266979</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.919425961427081</v>
+        <v>1.932624700381844</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1906048952712425</v>
+        <v>-0.1771997676184114</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.02477239695485878</v>
+        <v>0.03822969066507653</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.622170399260192</v>
+        <v>-1.607347415533567</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.202088875751407</v>
+        <v>-1.188532829399804</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.37253561070191</v>
+        <v>-1.382965246400062</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002288</t>
+          <t>X ≈ 0.002291</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.501387419296833</v>
+        <v>-2.664707836586942</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.486428557390987</v>
+        <v>-2.853871504321333</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.310303112668954</v>
+        <v>-4.119650932868637</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.675515946596967</v>
+        <v>-1.493840045276883</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.92968505038823</v>
+        <v>-2.745320924172333</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.561139837482671</v>
+        <v>-1.379288772009744</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.645406216020561</v>
+        <v>-1.821582867414982</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.3934734817327765</v>
+        <v>0.208871536662592</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6912461394670757</v>
+        <v>0.5048618922854402</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.632332713516462</v>
+        <v>1.439757456071163</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3530810440705849</v>
+        <v>0.164396517311765</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.820496990276354</v>
+        <v>1.626563748058587</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.400242379331452</v>
+        <v>1.206425153793653</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.649963711607661</v>
+        <v>1.432160804020107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003119</t>
+          <t>X ≈ 0.003121</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.665775462475999</v>
+        <v>-2.46875047347671</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.823922830324655</v>
+        <v>-2.6241888053518</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.400531036320601</v>
+        <v>-1.558439384723464</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1826358603575287</v>
+        <v>-0.3365990990240704</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.367851562959487</v>
+        <v>0.2179937779106211</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06318603749387819</v>
+        <v>-0.2148397914826603</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5104537646095295</v>
+        <v>-0.2998584371485364</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.927995456831667</v>
+        <v>2.148879883092249</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.684711221905744</v>
+        <v>3.912788432395651</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.017505193401625</v>
+        <v>1.239157329475482</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.630114849351394</v>
+        <v>2.858450769107641</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.301435406698481</v>
+        <v>2.527959429059045</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.517544432117333</v>
+        <v>1.743442880592362</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6763566734844488</v>
+        <v>0.8742880198699012</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00395</t>
+          <t>X ≈ 0.003952</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>256</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.32203116713444</v>
+        <v>3.334609904904177</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5340544490562493</v>
+        <v>0.5469642586323005</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1260576124695376</v>
+        <v>0.1390647438871397</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.775560789392074</v>
+        <v>3.788539931790538</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.0186921462372</v>
+        <v>4.031802950612139</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3632830562519729</v>
+        <v>-0.3483684036783501</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.890702640513155</v>
+        <v>1.903768894813631</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8672461541944472</v>
+        <v>0.6604808369894855</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.02122089752240441</v>
+        <v>0.03441963647716761</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4390343616033974</v>
+        <v>-0.4256292339505663</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1362038572490789</v>
+        <v>0.1496611509592967</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.165894138755988</v>
+        <v>-1.377705622587506</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4142737497009321</v>
+        <v>-0.4007177033493292</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2260725825754406</v>
+        <v>0.2156429468772885</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.004781</t>
+          <t>X ≈ 0.004782</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>218</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>8.260893993755481</v>
+        <v>8.268750239356528</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.350433190848911</v>
+        <v>4.363343000424962</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>8.991171574522888</v>
+        <v>9.00417870594049</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.294703107855426</v>
+        <v>7.30768225025389</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.005404103679076</v>
+        <v>4.018514908054016</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.939851931076547</v>
+        <v>5.692743621118765</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.313833810134497</v>
+        <v>6.326900064434973</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.305366007683268</v>
+        <v>6.318547016978506</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.785650525170695</v>
+        <v>5.798849264125458</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.476809743812439</v>
+        <v>4.49021487146527</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.272056419494959</v>
+        <v>4.285513713205177</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.058733154821994</v>
+        <v>7.072185443542104</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.344900562225718</v>
+        <v>4.35845660857732</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.888199876153436</v>
+        <v>6.877770240455284</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005612</t>
+          <t>X ≈ 0.005613</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>209</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.487422923809113</v>
+        <v>3.498186673695336</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9189115118017881</v>
+        <v>0.9318213213778392</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4328949938377562</v>
+        <v>-0.4198878624201541</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.216517459316456</v>
+        <v>-2.203538316917992</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.798000875345565</v>
+        <v>-1.784890070970626</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.849841234280653</v>
+        <v>-4.836798337986288</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.456106052031352</v>
+        <v>-4.443039797730876</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.401758350334376</v>
+        <v>-5.388577341039138</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.070413738909025</v>
+        <v>-3.057214999954262</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.442070024415422</v>
+        <v>-3.428664896762591</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.68988554968999</v>
+        <v>-2.676428255979772</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.61244019138757</v>
+        <v>-3.59898790266746</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.511163701854002</v>
+        <v>-4.497607655502399</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.69684906814242</v>
+        <v>-5.707278703840572</v>
       </c>
     </row>
     <row r="26">
@@ -1615,150 +1615,150 @@
         <v>172</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.9949337728132761</v>
+        <v>1.008312279501745</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5461508575234078</v>
+        <v>0.5590606670994589</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.895468197438483</v>
+        <v>1.908475328856085</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8812554141400355</v>
+        <v>-0.8682762717415713</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.419676629212205</v>
+        <v>-1.406565824837266</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.784742052689474</v>
+        <v>1.797784948983839</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.2814036842544</v>
+        <v>2.294469938554876</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.232824936635694</v>
+        <v>1.246005945930932</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.241592492313849</v>
+        <v>5.254791231268612</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.228676609611512</v>
+        <v>3.242081737264343</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.349504680642767</v>
+        <v>5.362961974352984</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.639701791476568</v>
+        <v>3.653154080196678</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.382237878206084</v>
+        <v>4.395793924557687</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.213354559319647</v>
+        <v>5.202924923621495</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.007273</t>
+          <t>X ≈ 0.007274</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>131</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.63847648814891</v>
+        <v>-4.039942173108315</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.856820127894558</v>
+        <v>0.8697299374706091</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.225310199923882</v>
+        <v>1.238317331341484</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.645639668409196</v>
+        <v>3.65861881080766</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.81714211745917</v>
+        <v>0.8302529218341093</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3512252765488739</v>
+        <v>0.3642681728432393</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.029850337902552</v>
+        <v>1.042916592203028</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2006918395049482</v>
+        <v>-0.1875108302097104</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.081819724694512</v>
+        <v>5.095018463649275</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.468335761040585</v>
+        <v>3.481740888693416</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.500223658097099</v>
+        <v>2.513680951807316</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2445304795646308</v>
+        <v>0.2579827682847409</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.641069761749492</v>
+        <v>3.654625808101095</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.216079134981854</v>
+        <v>-2.226508770680006</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.008103</t>
+          <t>X ≈ 0.008104</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>114</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.745494674858534</v>
+        <v>-2.732487543440932</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.246820489619466</v>
+        <v>-5.233841347221002</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.785241704691636</v>
+        <v>-5.772130900316697</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.487799766975975</v>
+        <v>-5.47475687068161</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.063761554423635</v>
+        <v>-2.050695300123159</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.916909865485792</v>
+        <v>-6.903728856190554</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.469137821843624</v>
+        <v>-3.455939082888861</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.196455989327653</v>
+        <v>-5.183050861674822</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.401209313645332</v>
+        <v>-5.387752019935114</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.858054226475282</v>
+        <v>-1.844601937755172</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.401115854964097</v>
+        <v>-1.387559808612494</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.028587505143896</v>
+        <v>-2.039017140842049</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>106</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.827316396771153</v>
+        <v>8.839838686446775</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>14.76291259512761</v>
+        <v>14.77582240470366</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.42464766211592</v>
+        <v>13.43765479353352</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.064334756987598</v>
+        <v>5.077313899386063</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.582517315500333</v>
+        <v>3.595628119875272</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.710147932461297</v>
+        <v>6.723190828755662</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.512206668019154</v>
+        <v>8.52527292231963</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.271438363577275</v>
+        <v>4.284619372872513</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.380249798149691</v>
+        <v>1.393448537104454</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.243460292538636</v>
+        <v>-3.230055164885805</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.268767515219338</v>
+        <v>1.282224808929556</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.470434233095631</v>
+        <v>-2.456981944375521</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.713084740865177</v>
+        <v>3.72664078721678</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.01940984672634</v>
+        <v>3.008980211028188</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>94</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.825710615960276</v>
+        <v>2.838232905635898</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.977352358706142</v>
+        <v>-1.964442549130091</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.883098083633428</v>
+        <v>1.89610521505103</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.077181003475005</v>
+        <v>3.090160145873469</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.602589575636884</v>
+        <v>3.615700380011823</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.482947210051741</v>
+        <v>-2.469904313757375</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.03486432610552</v>
+        <v>-3.021683316810282</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.159454936648338</v>
+        <v>1.172653675603101</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.436989326088536</v>
+        <v>2.450394453741367</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9592533599312034</v>
+        <v>-0.9457960662209857</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.394278733584464</v>
+        <v>4.407731022304574</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.910194335405521</v>
+        <v>2.923750381757124</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.287575242149863</v>
+        <v>5.277145606451711</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>61</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.604922335527704</v>
+        <v>1.617444625203326</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.911381509448695</v>
+        <v>4.924291319024746</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.07388985203245</v>
+        <v>11.08689698345005</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.925454460049792</v>
+        <v>7.938433602448256</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.387033244977623</v>
+        <v>7.400144049352562</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>14.24185223187361</v>
+        <v>14.25489512816797</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.51777425230625</v>
+        <v>12.53084050660672</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.05059085352475</v>
+        <v>12.06377186281998</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.710902442752314</v>
+        <v>8.724101181707077</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.13946578231452</v>
+        <v>11.15287090996735</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.656023933406786</v>
+        <v>7.669481227117004</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.051062828457127</v>
+        <v>6.064515117177237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.18818526669255</v>
+        <v>12.20174131304415</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.880529549788513</v>
+        <v>5.87009991409036</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.330091091554685</v>
+        <v>5.094841545223183</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.659693949178788</v>
+        <v>6.513958482462471</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.26482524258212</v>
+        <v>6.119187097707389</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.369627507163365</v>
+        <v>-5.871799879916374</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.908048722235449</v>
+        <v>-6.410089433012025</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.55178325510807</v>
+        <v>-9.143018433680012</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-10.57769344296858</v>
+        <v>-12.25803182324921</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>-3.634191376126857</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.282347316167723</v>
+        <v>-3.695173532649676</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-4.545092328979493</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-9.219578766689658</v>
+        <v>-10.81039954784575</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-9.185195609344227</v>
+        <v>-10.77602139549042</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.605450220289129</v>
+        <v>-11.19617224880383</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-9.355728888012877</v>
+        <v>-10.9704365985773</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>12.50656167979002</v>
+        <v>13.37274250605102</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.605011933174261</v>
+        <v>-0.4335655382323225</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.50011936022918</v>
+        <v>11.36678502823215</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.13037249283672</v>
+        <v>13.93603456206441</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.09195127776448</v>
+        <v>10.95872061872478</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>6.378045867872096</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.804659498207883</v>
+        <v>3.85431111836202</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>5.826266864819189</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>5.765284708296413</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.426351028216125</v>
+        <v>7.354390302210419</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.221597703898546</v>
+        <v>7.149689143950226</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.255980861244005</v>
+        <v>2.306018515817776</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.664273749700882</v>
+        <v>-0.5531567277395268</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.414552417424531</v>
+        <v>-0.3274210775129589</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>32</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.618438320209975</v>
+        <v>-5.605916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.230011933174254</v>
+        <v>-7.217102123598202</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.244627507163322</v>
+        <v>-1.231648364764858</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.605062082139447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.67965949820789</v>
+        <v>4.692725752508366</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.58747609942639</v>
+        <v>13.60065710872163</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.289674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.426351028216203</v>
+        <v>6.439756155869034</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.34659770389861</v>
+        <v>9.360054997608827</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.255980861244034</v>
+        <v>6.269433149964144</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.08572625029914</v>
+        <v>12.09928229665074</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.33544758257536</v>
+        <v>12.3250179468772</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,1093 +2210,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01059</t>
+          <t>X &gt; -0.01058</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0323095954349526</v>
+        <v>0.0319547711327246</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.101512472025675</v>
+        <v>0.1011298528608648</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.3087552777954201</v>
+        <v>0.3083190351837004</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1334399774992576</v>
+        <v>0.1330474154117809</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1238609488494404</v>
+        <v>0.1234669901149061</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1401911531182733</v>
+        <v>0.1397949728447401</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2408088105851007</v>
+        <v>0.2403871814305347</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3275276838036874</v>
+        <v>0.3270814702147504</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3293017660696478</v>
+        <v>0.3288545149598363</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2301111658421178</v>
+        <v>0.2296824457952837</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2358553243508936</v>
+        <v>0.2354236385525184</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2349579942658906</v>
+        <v>0.2345265619601946</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1975068700728499</v>
+        <v>0.1970816573588507</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.166013388233452</v>
+        <v>0.1662624131832047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.009757</t>
+          <t>X &gt; -0.009752</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.04209562496484409</v>
+        <v>-0.04249238521415322</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05960117673212295</v>
+        <v>0.05916666181694552</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2696534987551757</v>
+        <v>0.2691639485220847</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1175519800161595</v>
+        <v>0.1171007109068185</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1104469621048239</v>
+        <v>0.1099930486088709</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1747903541086799</v>
+        <v>0.1743226715772437</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2762854542898054</v>
+        <v>0.2757918600564651</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3902895248952944</v>
+        <v>0.3897639431652493</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3923735225504288</v>
+        <v>0.3918467192274804</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2720300405618445</v>
+        <v>0.2715260892187885</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3034697710756689</v>
+        <v>0.3029562321766974</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3271271063033012</v>
+        <v>0.3266077609791935</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2173669718212281</v>
+        <v>0.2168712294570341</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2092735835640269</v>
+        <v>0.2095620536229816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.008926</t>
+          <t>X &gt; -0.008922</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.08290154088592061</v>
+        <v>-0.08340050258404119</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03369052767587277</v>
+        <v>0.03314638534813952</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.19927400965733</v>
+        <v>0.1986845329095175</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.09443615859147059</v>
+        <v>0.09387376352951549</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.04220003398340566</v>
+        <v>0.04164502170671369</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07961466360158909</v>
+        <v>0.07905302719741769</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2075962826777698</v>
+        <v>0.2070016917967479</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3017529229265179</v>
+        <v>0.3011299807972918</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3292650578656051</v>
+        <v>0.3286343746534186</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1654543906071879</v>
+        <v>0.1648557574626111</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1989270511830838</v>
+        <v>0.1983177622414232</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3470598545158836</v>
+        <v>0.346413717976084</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2150881645563416</v>
+        <v>0.2144704352004325</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2296759545524623</v>
+        <v>0.2300528421913057</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.008095</t>
+          <t>X &gt; -0.008091</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3968</v>
+        <v>3969</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.03105301362574409</v>
+        <v>0.03038482330794068</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.09096796632326232</v>
+        <v>0.0902641160400961</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3128863871203507</v>
+        <v>0.3121214665211482</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1049828497999741</v>
+        <v>0.1042714643379341</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03286151160911999</v>
+        <v>0.03216112688555484</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06746162594294702</v>
+        <v>0.06675595084921326</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2480557246229864</v>
+        <v>0.2473032172971017</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3231328684248851</v>
+        <v>0.3223552219291719</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4271180456125734</v>
+        <v>0.4263131001605984</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2455856707136448</v>
+        <v>0.2448153051264796</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.332023289393419</v>
+        <v>0.3312282100962065</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4310438335362008</v>
+        <v>0.430223882777014</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2518260235417458</v>
+        <v>0.2510455208320721</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.289076614833462</v>
+        <v>0.2895556137958621</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007265</t>
+          <t>X &gt; -0.007261</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1019815271182622</v>
+        <v>0.10112416280068</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.08180405053663264</v>
+        <v>0.08092586622370845</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4390195638951653</v>
+        <v>0.4380437733978653</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1248975755970605</v>
+        <v>0.124003366396046</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03336747745885305</v>
+        <v>0.03248759780025523</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2683741071999108</v>
+        <v>0.2674386588962889</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4779520568215503</v>
+        <v>0.4769614212981708</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5091559362859357</v>
+        <v>0.5081494634616845</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6153339388942669</v>
+        <v>0.6142989644343828</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4680495745053719</v>
+        <v>0.4670381548491065</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4562915814496051</v>
+        <v>0.4552794301515206</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.556184994951586</v>
+        <v>0.555147435678407</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4056598899111563</v>
+        <v>0.4046535648313707</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4146536075945519</v>
+        <v>0.415242551267248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.006434</t>
+          <t>X &gt; -0.00643</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06035996861554338</v>
+        <v>0.05926022659369323</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.122166490062277</v>
+        <v>0.1210168808093925</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4676939386987016</v>
+        <v>0.4664459937214716</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.09326818562339412</v>
+        <v>0.092119469216982</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.01019680073361684</v>
+        <v>0.009057930608570075</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2180536516172324</v>
+        <v>0.2168664258155388</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4851321027261974</v>
+        <v>0.4838732083754564</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.4738397357900297</v>
+        <v>0.4725734940760802</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5312177045405306</v>
+        <v>0.5299346924585961</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3452699471350726</v>
+        <v>0.3440170028422358</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.311148002832816</v>
+        <v>0.309899072452879</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5682533521436497</v>
+        <v>0.5669376989633435</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3708367834590618</v>
+        <v>0.3695631078831596</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4532935763319017</v>
+        <v>0.4540816659929732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.005603</t>
+          <t>X &gt; -0.0056</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3767</v>
+        <v>3768</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.07216285050899529</v>
+        <v>-0.07350862312694773</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1611262793891584</v>
+        <v>-0.1624911153949569</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4379006681455095</v>
+        <v>0.4363663010697536</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2384233402943039</v>
+        <v>0.236944433752484</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1647989598837185</v>
+        <v>0.1633247940038487</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3443481704351257</v>
+        <v>0.3428334627679064</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6040765623308388</v>
+        <v>0.6171428166313149</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5756155110351884</v>
+        <v>0.5740275379744091</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6354369767647725</v>
+        <v>0.6338307963546939</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.51611501654817</v>
+        <v>0.5145175556569015</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3794226375855914</v>
+        <v>0.3778553158267783</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5614995664708644</v>
+        <v>0.5598840783460872</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4217135114456099</v>
+        <v>0.420123368553071</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4476721644708022</v>
+        <v>0.4486909829706676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.004772</t>
+          <t>X &gt; -0.004769</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3665</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.06368899208599288</v>
+        <v>0.07621128176161562</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04464793077134033</v>
+        <v>0.05755774034739147</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5477384078482217</v>
+        <v>0.5757285602368754</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3391367824392972</v>
+        <v>0.3521159248377614</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2784473300378565</v>
+        <v>0.2915581344127958</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.345820230730709</v>
+        <v>0.3588631270250744</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.587883899079344</v>
+        <v>0.6160095988717629</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4354058188488921</v>
+        <v>0.4485868281441299</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5802909271405454</v>
+        <v>0.5934896660953086</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4267598589602386</v>
+        <v>0.4401649866130697</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.18288450869683</v>
+        <v>0.1963418024070478</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.314475543545619</v>
+        <v>0.3279278322657291</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3188140844507785</v>
+        <v>0.3323701308023814</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3930874188646243</v>
+        <v>0.4099429127708305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.003942</t>
+          <t>X &gt; -0.003939</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4543438246524545</v>
+        <v>0.4520056646663235</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2336569800523876</v>
+        <v>0.2313116888667253</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7374122554833207</v>
+        <v>0.7504193869009228</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5741927175557748</v>
+        <v>0.5717425366673226</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6412628821477639</v>
+        <v>0.6387699473079849</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3922037832148533</v>
+        <v>0.3897921106506175</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7852665808385879</v>
+        <v>0.7983328351390639</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5585893971491913</v>
+        <v>0.5561096101269101</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7944739635252986</v>
+        <v>0.7919240385075383</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4945648116198171</v>
+        <v>0.4920621176237674</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2335526968662336</v>
+        <v>0.2470099905764513</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3682487284359155</v>
+        <v>0.365776328585774</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4986871284302623</v>
+        <v>0.4961590552325887</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6237358708636833</v>
+        <v>0.6253979074739178</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003111</t>
+          <t>X &gt; -0.003108</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3404</v>
+        <v>3401</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6855830685975235</v>
+        <v>0.6706524244641798</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4670865427929485</v>
+        <v>0.4826779350528483</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9221592195492292</v>
+        <v>0.9546049310718345</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9220758056481699</v>
+        <v>0.9381594967781126</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.8984028906677395</v>
+        <v>0.9149212370690236</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6842010770231397</v>
+        <v>0.7003521669550423</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.039479093397091</v>
+        <v>1.042916592203028</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8527343153888296</v>
+        <v>0.8400875256329599</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.042986339454835</v>
+        <v>1.030497272316332</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7085001767775267</v>
+        <v>0.7258901159159947</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5331068054840173</v>
+        <v>0.5672618738944308</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.554806118219048</v>
+        <v>0.5722541902227221</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6506498695705503</v>
+        <v>0.6685062825413652</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8416167952663542</v>
+        <v>0.8522893376446703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.00228</t>
+          <t>X &gt; -0.002277</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7903287182039023</v>
+        <v>0.7718720735548672</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5277739360541531</v>
+        <v>0.5096952113878785</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.155526859454461</v>
+        <v>1.154787991956759</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.334030273369841</v>
+        <v>1.316011275656713</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9059047661366009</v>
+        <v>0.8880078185735556</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6933634388052283</v>
+        <v>0.675388965372548</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.011855527984565</v>
+        <v>1.011179056883172</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7791453516758509</v>
+        <v>0.7612993674867568</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.201057218830684</v>
+        <v>1.183219334570047</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8651898981323356</v>
+        <v>0.8475487668593615</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6914828327405615</v>
+        <v>0.6915767367392363</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6814466997533302</v>
+        <v>0.6638430878523209</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8691217147290615</v>
+        <v>0.8516122127737304</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.056711950391488</v>
+        <v>1.033066424192349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.00145</t>
+          <t>X &gt; -0.001447</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.84427953575846</v>
+        <v>0.8414523905182847</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3686722773520827</v>
+        <v>0.3666013972968543</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.223803570755493</v>
+        <v>1.240578762877853</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.339487333244705</v>
+        <v>1.337887514102825</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.016901903175963</v>
+        <v>1.01550001430936</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9376316086313068</v>
+        <v>0.9360329497191984</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.280951892017569</v>
+        <v>1.297956395012477</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8980821600324447</v>
+        <v>0.896785609545347</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.415685438944244</v>
+        <v>1.381632763668854</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.092743120473159</v>
+        <v>1.077903204995266</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.8879897961555798</v>
+        <v>0.8732020467350736</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8423355085742728</v>
+        <v>0.8086682307422279</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.034374453398357</v>
+        <v>1.033978866571559</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.086271848978306</v>
+        <v>1.080791618932672</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0006189</t>
+          <t>X &gt; -0.0006164</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2807</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7570057295235912</v>
+        <v>0.750618060374741</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1238437882187995</v>
+        <v>0.1174893506469274</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8661463680472323</v>
+        <v>0.8791534994648345</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.016081700088719</v>
+        <v>1.009378643053196</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7818517045070408</v>
+        <v>0.7751651749229538</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7433597754232508</v>
+        <v>0.7367177618456608</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.227818516350901</v>
+        <v>1.240884770651377</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.029646917931728</v>
+        <v>1.022837827327109</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.593848943753166</v>
+        <v>1.586827977109877</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.064122477130368</v>
+        <v>1.077527604783199</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9661687256145015</v>
+        <v>0.9796260193247193</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9853255905887437</v>
+        <v>0.9784043140794623</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.333588736939653</v>
+        <v>1.326490273858695</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.36955873327009</v>
+        <v>1.359129097571937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002119</t>
+          <t>X &gt; 0.0002141</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2547</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9730716680391467</v>
+        <v>0.9646595372025288</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4796275652583617</v>
+        <v>0.4711567874868194</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.417047259915698</v>
+        <v>1.4300543913333</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.530019690014257</v>
+        <v>1.521094581943608</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.405676767960585</v>
+        <v>1.396712415342115</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.019051905162392</v>
+        <v>1.010279249029431</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.679708537046658</v>
+        <v>1.692774791347134</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.509375628468781</v>
+        <v>1.500323644618057</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.311798034280201</v>
+        <v>2.324996773234965</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.54016578488806</v>
+        <v>1.553570912540891</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.649384203113655</v>
+        <v>1.662841496823873</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.510201512991166</v>
+        <v>1.500987310089705</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.718136929529578</v>
+        <v>1.731692975881181</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.535977617911087</v>
+        <v>1.525547982212935</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.001043</t>
+          <t>X &gt; 0.001045</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2343</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.126663894440789</v>
+        <v>1.116359405821541</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.39008819464852</v>
+        <v>0.3797888474409987</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.316054596701271</v>
+        <v>1.329061728118873</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.427473942112044</v>
+        <v>1.416679287557258</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9316784729904271</v>
+        <v>0.9447892773653663</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.442698119531336</v>
+        <v>0.4322741339399272</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.381418560041581</v>
+        <v>1.394484814342057</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.06614504140591</v>
+        <v>1.055347940278132</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.114360172288457</v>
+        <v>2.12755891124322</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.264234987260529</v>
+        <v>1.27764011491336</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.400778591270601</v>
+        <v>1.414235884980819</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.289058112631125</v>
+        <v>1.277965573172317</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.594369015984128</v>
+        <v>1.607925062335731</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.374606780185303</v>
+        <v>1.364177144487151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001873</t>
+          <t>X &gt; 0.001875</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2105</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.608031570733601</v>
+        <v>1.594913353351899</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9708893950990145</v>
+        <v>0.9576845051358163</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.999170593625756</v>
+        <v>2.012177725043358</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.939670405550153</v>
+        <v>1.952649547948617</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.353810860307206</v>
+        <v>1.366921664682145</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.060964169443146</v>
+        <v>1.047597402097111</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.403378055398207</v>
+        <v>1.416444309698683</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.200249128866083</v>
+        <v>1.186679889927134</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.136400239834778</v>
+        <v>2.149598978789541</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.428725197256995</v>
+        <v>1.442130324909826</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.556355538656412</v>
+        <v>1.56981283236663</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.618213640341402</v>
+        <v>1.604190984721953</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.910548103030706</v>
+        <v>1.924104149382309</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.685210052884187</v>
+        <v>1.674780417186035</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002704</t>
+          <t>X &gt; 0.002706</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.235921985968268</v>
+        <v>2.248444275643891</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.499143342932925</v>
+        <v>1.542471180559374</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.9632139474353</v>
+        <v>2.952951436942186</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.492045538216665</v>
+        <v>2.481426033484588</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.008299008765057</v>
+        <v>1.99784107557489</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.461603281125683</v>
+        <v>1.419941582234053</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.869210920527365</v>
+        <v>1.913237520433931</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.323518792365633</v>
+        <v>1.33669980166087</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.3572096560465</v>
+        <v>2.401942203020319</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.397615396032251</v>
+        <v>1.442494381498783</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.740207446646252</v>
+        <v>1.785438349196973</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.587306162448826</v>
+        <v>1.600758451168936</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.988519240441498</v>
+        <v>2.03421380350003</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.690595446759403</v>
+        <v>1.712004248247112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003535</t>
+          <t>X &gt; 0.003536</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1551</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.105017278245626</v>
+        <v>3.081784934095879</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.265644437482138</v>
+        <v>2.278554247058189</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.736927597037415</v>
+        <v>3.749934728455017</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.966279828744007</v>
+        <v>2.979258971142471</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.29915848497172</v>
+        <v>2.312269289346659</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.731955997192983</v>
+        <v>1.708742418080845</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.29113728314028</v>
+        <v>2.304203537440756</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.216342078807834</v>
+        <v>1.193219890434442</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.121837037986353</v>
+        <v>2.135035776941116</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.465010822030592</v>
+        <v>1.478415949683423</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.582422446166625</v>
+        <v>1.595879739876843</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.460687502120869</v>
+        <v>1.436958923159992</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.072025412130181</v>
+        <v>2.085581458481784</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.870425016489008</v>
+        <v>1.859995380790856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004365</t>
+          <t>X &gt; 0.004367</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1295</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.031805634847295</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.60795102978873</v>
+        <v>2.620860839364781</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.450736644179791</v>
+        <v>4.463743775597393</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.806298418762609</v>
+        <v>2.819277561161073</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.959235228381793</v>
+        <v>1.972346032756732</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.146149972236927</v>
+        <v>2.115399074737496</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.370296563844953</v>
+        <v>2.383362818145429</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.285352547302836</v>
+        <v>1.298533556598073</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.53709397386185</v>
+        <v>2.550292712816614</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.841408943274068</v>
+        <v>1.854814070926899</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.868315850616725</v>
+        <v>1.881773144326942</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.979919085182232</v>
+        <v>1.993371373902342</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.563525478098335</v>
+        <v>2.577081524449937</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.195486192614005</v>
+        <v>2.185056556915853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005196</t>
+          <t>X &gt; 0.005197</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1077</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.009811447663743</v>
+        <v>1.971774136441532</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.255248048255659</v>
+        <v>2.26815785783171</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.531688533859636</v>
+        <v>3.544695665277239</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.89778196358877</v>
+        <v>1.910761105987234</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.545061769872213</v>
+        <v>1.558172574247152</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.378251154198828</v>
+        <v>1.391294050493194</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.572068968959982</v>
+        <v>1.585135223260458</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.269230974078198</v>
+        <v>0.2824119833734358</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.879540280096457</v>
+        <v>1.89273901905122</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.307966627101955</v>
+        <v>1.321371754754786</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.381764834817794</v>
+        <v>1.395222128528012</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9518954387741871</v>
+        <v>0.9653477274942972</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.202950020029846</v>
+        <v>2.216506066381449</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.245614713494611</v>
+        <v>1.235185077796459</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.006027</t>
+          <t>X &gt; 0.006028</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>868</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.654027117578046</v>
+        <v>1.604239320443781</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.577015716595355</v>
+        <v>2.589925526171406</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.486294475436551</v>
+        <v>4.499301606854154</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.888437008965717</v>
+        <v>2.901416151364181</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.350015793893547</v>
+        <v>2.363126598268487</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.87787247815298</v>
+        <v>2.890915374447346</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.023553507424481</v>
+        <v>3.036619761724957</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.634711122467863</v>
+        <v>1.647892131763101</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.071407088820123</v>
+        <v>3.084605827774887</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.451696650335975</v>
+        <v>2.465101777988806</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.362150699290282</v>
+        <v>2.3756079930005</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.050911736820048</v>
+        <v>2.064364025540158</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.819597218041046</v>
+        <v>3.833153264392649</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.917244817598444</v>
+        <v>2.906815181900292</v>
       </c>
     </row>
     <row r="27">
@@ -3309,98 +3309,98 @@
         <v>696</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.816906507376231</v>
+        <v>1.751508646653598</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.078896112802788</v>
+        <v>3.091805922378839</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.126556141838371</v>
+        <v>5.139563273255973</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.820027665250471</v>
+        <v>3.833006807648935</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.281606450178302</v>
+        <v>3.294717254553241</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.148013905135343</v>
+        <v>3.161056801429709</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.206958348782599</v>
+        <v>3.220024603083075</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.734027823564325</v>
+        <v>1.747208832859563</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.535096902899262</v>
+        <v>2.548295641854025</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.623896554473291</v>
+        <v>1.637353848183508</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.658279711818722</v>
+        <v>1.671732000538832</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.680553836506007</v>
+        <v>3.69410988285761</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.349815398667353</v>
+        <v>2.339385762969201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.007688</t>
+          <t>X &gt; 0.007689</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>565</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.081782918728081</v>
+        <v>3.094305208403703</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.594103111073551</v>
+        <v>3.607012920649602</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.031092811556604</v>
+        <v>6.044099942974206</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.860460988411894</v>
+        <v>3.873440130810359</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.853013224667166</v>
+        <v>3.866124029042105</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.796472861497868</v>
+        <v>3.809515757792234</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.711739144225589</v>
+        <v>3.724805398526065</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.182608842789229</v>
+        <v>2.195789852084467</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.944617806164437</v>
+        <v>1.957816545119201</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.979448373348902</v>
+        <v>1.992853501001733</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.420712748146364</v>
+        <v>1.434170041856582</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.986069356819229</v>
+        <v>1.999521645539339</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.689708551184069</v>
+        <v>3.703264597535671</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.408456432132922</v>
+        <v>3.39802679643477</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>451</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.491040615488473</v>
+        <v>4.503562905164095</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.540220882790287</v>
+        <v>5.553130692366338</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.249565036504116</v>
+        <v>8.262572167921718</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.162523268889892</v>
+        <v>6.175502411288356</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.28929052388424</v>
+        <v>6.30240132825918</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.143273481555561</v>
+        <v>6.156316377849926</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.171621804194579</v>
+        <v>5.184688058495055</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.482708915390909</v>
+        <v>4.495889924686146</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.313061579097742</v>
+        <v>3.326260318052505</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.79331333420285</v>
+        <v>3.806718461855681</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.14510102984093</v>
+        <v>3.158558323551148</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.957754697164191</v>
+        <v>2.971206985884301</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.976524476463197</v>
+        <v>4.9900805228148</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.78278682869513</v>
+        <v>4.772357192996978</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>345</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.158735592833501</v>
+        <v>3.171257882509124</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.706582269724322</v>
+        <v>2.719492079300373</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.659539650084248</v>
+        <v>6.67254678150185</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.499937710227989</v>
+        <v>6.512916852626454</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.12093678501089</v>
+        <v>7.13404758938583</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.969103360407701</v>
+        <v>5.982146256702066</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.145239208352812</v>
+        <v>4.158305462653288</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.547621026962624</v>
+        <v>4.560802036257861</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.906910995852783</v>
+        <v>3.920109734807546</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.955336535462543</v>
+        <v>5.968741663115374</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.625546078635324</v>
+        <v>4.638998367355434</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.364711757545493</v>
+        <v>5.378267803897096</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.324578017358007</v>
+        <v>5.314148381659855</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>251</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.283454110068902</v>
+        <v>3.295976399744525</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.460725118618598</v>
+        <v>4.473634928194649</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.44832653154392</v>
+        <v>8.461333662961522</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.781766915147436</v>
+        <v>7.7947460575459</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.438564823581238</v>
+        <v>8.451675627956178</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.134413135798894</v>
+        <v>9.14745603209326</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.456053920518649</v>
+        <v>7.469120174819125</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.387276896239136</v>
+        <v>7.400457905534374</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.935838763044885</v>
+        <v>4.949037501999648</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.272964574032891</v>
+        <v>7.286369701685722</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.474585751707345</v>
+        <v>5.488043045417562</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.712156160048792</v>
+        <v>4.725608448768902</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.283933421613852</v>
+        <v>6.297489467965455</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.338435630384161</v>
+        <v>5.328005994686009</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.82235115347423</v>
+        <v>3.834873443149853</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.31604069840472</v>
+        <v>4.328950507980771</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.605382518123918</v>
+        <v>7.61838964954152</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.735635650731417</v>
+        <v>7.748614793129882</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.776161804080296</v>
+        <v>8.789272608455235</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.494656373374909</v>
+        <v>7.507699269669274</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.830975287681575</v>
+        <v>5.844041541982051</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.890107678373759</v>
+        <v>5.903288687668997</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.723844634296711</v>
+        <v>3.737043373251474</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.0316141861109</v>
+        <v>6.045019313763731</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.774229282845951</v>
+        <v>4.787686576556169</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.282296650717697</v>
+        <v>4.295748939437807</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.38835782924648</v>
+        <v>4.401913875598083</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.164394950996453</v>
+        <v>5.153965315298301</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.275792449020798</v>
+        <v>3.570039383478388</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.587295759133454</v>
+        <v>3.869681315892265</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.67960653971636</v>
+        <v>7.93350865725187</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.37396223642643</v>
+        <v>10.61150450147718</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.98404297385918</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.77400860009556</v>
+        <v>11.0075316531758</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.407223600771992</v>
+        <v>9.648935943591169</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.657988919939207</v>
+        <v>7.907981949485958</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.032886469654343</v>
+        <v>5.299229092326236</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.028915130780263</v>
+        <v>8.270966346951795</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.824161806462683</v>
+        <v>8.066265188691602</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.217519322782472</v>
+        <v>7.463700665887686</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.438290352863213</v>
+        <v>7.680492487733517</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.32903732616515</v>
+        <v>8.543170813119282</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>116</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>0.1052908660173699</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.377746687515426</v>
+        <v>5.390656497091477</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.707015911953313</v>
+        <v>6.720023043370915</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.423475941112542</v>
+        <v>9.436455083511007</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.33333058810933</v>
+        <v>12.34644139248427</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.63077252582499</v>
+        <v>12.64381542211936</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.68396984303548</v>
+        <v>11.69703609733595</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.630579547702254</v>
+        <v>8.643760556997492</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.121303799450985</v>
+        <v>5.134502538405748</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.581523442009271</v>
+        <v>8.594928569662102</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.376770117691692</v>
+        <v>8.390227411401909</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.273222240554361</v>
+        <v>9.286674529274471</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.57710556064394</v>
+        <v>10.59066160699554</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.68889585843746</v>
+        <v>11.67846622273931</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>10.18070235254006</v>
+        <v>10.19361216211611</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.97630983641966</v>
+        <v>10.98931696783726</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.48751534997954</v>
+        <v>13.500494492378</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.13957032538356</v>
+        <v>14.1526811297585</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.43701226309922</v>
+        <v>14.45005515939359</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.35227854582694</v>
+        <v>14.36534480012742</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.742238004188295</v>
+        <v>6.755419013483532</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.402541504406642</v>
+        <v>9.415946632059473</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.007311989612873</v>
+        <v>8.020769283323091</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.44259043971826</v>
+        <v>11.43216080402011</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Hash Rate MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Hash Rate MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,1093 +3904,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01059</t>
+          <t>X &lt; -0.01058</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-14.02369016358035</v>
+        <v>-14.01068303216275</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.216611507273079</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.73395247200218</v>
+        <v>-8.720771462706942</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.413999977232102</v>
+        <v>-6.400801238277339</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.897449915149032</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.009757</t>
+          <t>X &lt; -0.009752</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.846367505032738</v>
+        <v>2.858889794708361</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2639201056607163</v>
+        <v>0.2768299152367675</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.839686465013536</v>
+        <v>-9.826679333595933</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.913316827551675</v>
+        <v>-2.900337685153211</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.480864256216073</v>
+        <v>-2.467753451841133</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.154296104908184</v>
+        <v>-3.141253208613819</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.180777394995992</v>
+        <v>-5.167711140695516</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.531455939408559</v>
+        <v>-9.518274930113321</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.650708252775331</v>
+        <v>-7.637509513820568</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.64646450576442</v>
+        <v>-3.633059378111589</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.792965402897536</v>
+        <v>-5.779508109187319</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.758582245552105</v>
+        <v>-5.745129956831995</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.324467924458176</v>
+        <v>-1.310911878106573</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.074746592181889</v>
+        <v>-1.085176227880041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.008926</t>
+          <t>X &lt; -0.008922</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.303663129065392</v>
+        <v>3.316185418741014</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9674518349417127</v>
+        <v>0.9803616445177639</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.224518320930237</v>
+        <v>-5.211511189512635</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.471076782525643</v>
+        <v>-1.458097640127178</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1644150458804532</v>
+        <v>0.1775258502553925</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4618569835961139</v>
+        <v>0.4748998798904793</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.79678977715443</v>
+        <v>-1.783723522853954</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.437886219414189</v>
+        <v>-4.424705210118951</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.774248424437076</v>
+        <v>-3.761049685482313</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.205938527985474</v>
+        <v>-1.192481234275256</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.794743776437151</v>
+        <v>-4.781291487717041</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8671723004255227</v>
+        <v>-0.8536162540739198</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.342088649308657</v>
+        <v>-1.352518285006809</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.008095</t>
+          <t>X &lt; -0.008091</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>181</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.007250474906108195</v>
+        <v>0.005271814769514549</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5138517121797577</v>
+        <v>-0.5009419026037065</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.433582297229385</v>
+        <v>-6.420575165811783</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.330953474014152</v>
+        <v>-1.317974331615687</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3405700622949013</v>
+        <v>0.3536808666698406</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.638012000010562</v>
+        <v>0.6510548963049274</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.209152656488243</v>
+        <v>-2.196086402187767</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.781308430960351</v>
+        <v>-3.768127421665113</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.947280692833253</v>
+        <v>-4.93408195387849</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.37751637509875</v>
+        <v>-1.364111247445919</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.792214450797552</v>
+        <v>-3.778757157087334</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.415289856988025</v>
+        <v>-5.401837568267915</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.415654965170496</v>
+        <v>-1.402098918818893</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.270906008584831</v>
+        <v>-2.281335644282983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007265</t>
+          <t>X &lt; -0.007261</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>232</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.20033487193411</v>
+        <v>-1.187812582258488</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.225701588346638</v>
+        <v>-0.2127917787705869</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.086087536322545</v>
+        <v>-7.073080404904942</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.352386127852981</v>
+        <v>-1.339406985454517</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.264365070867953</v>
+        <v>0.2774758752428923</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.886468853485347</v>
+        <v>-2.873425957190982</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.557409467309355</v>
+        <v>-5.544343213008879</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.024592866090856</v>
+        <v>-6.011411856795618</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6.947661717790396</v>
+        <v>-6.934462978835633</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.780545523507975</v>
+        <v>-4.767140395855144</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.985298847825554</v>
+        <v>-4.971841554115336</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.647032370390548</v>
+        <v>-3.633476324038945</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.82834552087288</v>
+        <v>-3.838775156571032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.006434</t>
+          <t>X &lt; -0.00643</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>305</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3622907792263703</v>
+        <v>-0.3497684895507476</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6623889823545568</v>
+        <v>-0.6494791727785056</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.647421623377383</v>
+        <v>-5.634414491959781</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5991357038846346</v>
+        <v>-0.5861565614861703</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5017873433382789</v>
+        <v>0.5148981477132182</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.495852686159182</v>
+        <v>-1.482809789864817</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.203537223103581</v>
+        <v>-4.190470968803105</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.014982916967057</v>
+        <v>-4.001801907671819</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.075982803149358</v>
+        <v>-4.062784064194595</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.975288316046132</v>
+        <v>-1.961883188393301</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.852172787904699</v>
+        <v>-1.838715494194481</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.768609302690408</v>
+        <v>-4.755157013970297</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.23804424150417</v>
+        <v>-2.224488195152567</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.299798319063953</v>
+        <v>-3.310227954762105</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.005603</t>
+          <t>X &lt; -0.0056</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>382</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.031365857335715</v>
+        <v>1.043888147011337</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.291854907556839</v>
+        <v>2.30476471713289</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.108235731154636</v>
+        <v>-4.095228599737034</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.889209752594134</v>
+        <v>-1.87623061019567</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.122147938945673</v>
+        <v>-1.109037134570734</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.391285635694757</v>
+        <v>-2.378242739400392</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.433560397080072</v>
+        <v>-4.551725944619577</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.115403481725444</v>
+        <v>-4.102222472430206</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.176403367907746</v>
+        <v>-4.163204628952982</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.194067819951385</v>
+        <v>-3.180662692298554</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.089920620708746</v>
+        <v>-2.076463326998528</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.626218091635572</v>
+        <v>-3.612765802915462</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.214011969596179</v>
+        <v>-2.200455923244576</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.487850846743981</v>
+        <v>-2.498280482442134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.004772</t>
+          <t>X &lt; -0.004769</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2300638346132757</v>
+        <v>-0.3248585356678291</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.215975721146755</v>
+        <v>0.1173434616174305</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.984416722245051</v>
+        <v>-4.178865294800865</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.204679053555068</v>
+        <v>-2.299035196040577</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.712172433575695</v>
+        <v>-1.808518164774128</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.827101629880652</v>
+        <v>-1.9226667688839</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.249059510056576</v>
+        <v>-3.447706346257064</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.063350346854605</v>
+        <v>-2.159652169628885</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.744184943780702</v>
+        <v>-2.839191027182586</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.734805996577222</v>
+        <v>-1.833439720419669</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.08005518866340111</v>
+        <v>-0.1824707755870776</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.872118312309702</v>
+        <v>-0.9728348912729885</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.8791497827587378</v>
+        <v>-0.9806146105657803</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.455874731474196</v>
+        <v>-1.579621228380482</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.003942</t>
+          <t>X &lt; -0.003939</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>597</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.938345266507568</v>
+        <v>-0.9254354569315169</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.249463277500375</v>
+        <v>-4.320206841686549</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.117540695811073</v>
+        <v>-3.104561553412609</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.48901700270293</v>
+        <v>-3.475906198327991</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.689070891364572</v>
+        <v>-1.676027995070207</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.691996020186757</v>
+        <v>-3.764077252499987</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.319714536025117</v>
+        <v>-2.306533526729879</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.384058903812772</v>
+        <v>-3.370860164858009</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.725822884827323</v>
+        <v>-1.712417757174492</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.332003636134921</v>
+        <v>-0.4121021930266551</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9676372292082505</v>
+        <v>-0.9541849404881404</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.722900215362536</v>
+        <v>-1.709344169010933</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.478204008714378</v>
+        <v>-2.488633644412531</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003111</t>
+          <t>X &lt; -0.003108</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.960728039836141</v>
+        <v>-2.879852200747116</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.768563335043396</v>
+        <v>-1.831463825725841</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.09881112105424</v>
+        <v>-4.220916061544713</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.96855798844674</v>
+        <v>-4.02375888407245</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.838530005657944</v>
+        <v>-3.896269475783321</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.605259190936948</v>
+        <v>-2.666804900209485</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.959062054670291</v>
+        <v>-3.949917389968334</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.087557367775752</v>
+        <v>-3.01600955794504</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.684032488228475</v>
+        <v>-3.610325047801147</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.258387927607131</v>
+        <v>-2.326910510797674</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.586713288058519</v>
+        <v>-1.73161166905787</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.552330130713088</v>
+        <v>-1.624425328006502</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.97258474165799</v>
+        <v>-2.044576181319911</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.857505437558828</v>
+        <v>-2.88693131881034</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.00228</t>
+          <t>X &lt; -0.002277</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.60050470136629</v>
+        <v>-2.534391966363231</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.535418785422628</v>
+        <v>-1.471781267983204</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.910384391110583</v>
+        <v>-3.898638214235575</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.423218075223339</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.925197704014707</v>
+        <v>-2.860676675890524</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.984668949578783</v>
+        <v>-1.920904359317547</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.871306167028166</v>
+        <v>-2.862145767834242</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.050935917740993</v>
+        <v>-1.987499375737109</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.292193314652913</v>
+        <v>-3.227474029580364</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.210988027577834</v>
+        <v>-2.148132375749448</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.713418407809257</v>
+        <v>-1.709746717289377</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.571623864856953</v>
+        <v>-1.509536807117428</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.206701247015609</v>
+        <v>-2.144279935108941</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.866165320650403</v>
+        <v>-2.776913383594859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.00145</t>
+          <t>X &lt; -0.001447</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.181217089166267</v>
+        <v>-2.169250847987605</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.759784457705905</v>
+        <v>-0.7528323105972916</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.249880639770829</v>
+        <v>-3.284736375672892</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.476770364306184</v>
+        <v>-3.465382767616909</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.586620150806915</v>
+        <v>-2.57764736527588</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.199892498805539</v>
+        <v>-2.191146775926001</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.952713155947606</v>
+        <v>-2.988869612910527</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.900682971172358</v>
+        <v>-1.893321481822525</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.123434421250991</v>
+        <v>-3.024776430495173</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.316940563912638</v>
+        <v>-2.268986038600232</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.84688931490178</v>
+        <v>-1.800659288105493</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.633455128012933</v>
+        <v>-1.538877841992978</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.143235253729536</v>
+        <v>-2.137759705136602</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.292688618141447</v>
+        <v>-2.269486074570473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0006189</t>
+          <t>X &lt; -0.0006164</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.491211148717767</v>
+        <v>-1.478688859042144</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.05898372233532712</v>
+        <v>-0.04607391275927597</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.750995052846598</v>
+        <v>-1.777148192837252</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.992212945499126</v>
+        <v>-1.979233803100662</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.490515289843216</v>
+        <v>-1.477404485468277</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.267367557179561</v>
+        <v>-1.254324660885196</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.130284739710326</v>
+        <v>-2.156271275723427</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.705274829941636</v>
+        <v>-1.692093820646399</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.732817467053302</v>
+        <v>-2.719618728098538</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.683768019402883</v>
+        <v>-1.710801464948851</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.550181894016539</v>
+        <v>-1.577445002391201</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.515798736671108</v>
+        <v>-1.502346447950998</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.233894002865448</v>
+        <v>-2.220337956513845</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.316191761686895</v>
+        <v>-2.292442961536757</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002119</t>
+          <t>X &lt; 0.0002141</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.467956654579154</v>
+        <v>-1.455434364903532</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.5935141084383702</v>
+        <v>-0.580604298862319</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.198885614895204</v>
+        <v>-2.218383763169875</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.317388701193167</v>
+        <v>-2.304409558794703</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.109541259548919</v>
+        <v>-2.09643045517398</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.376775938748686</v>
+        <v>-1.363733042454321</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.299571989035421</v>
+        <v>-2.319090167889648</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.02002234487977</v>
+        <v>-2.006841335584532</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.168729266207968</v>
+        <v>-3.187923056513036</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.99265208704864</v>
+        <v>-2.012921303657777</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.22603321879469</v>
+        <v>-2.246253413606148</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.942273502845765</v>
+        <v>-1.928821214125655</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.266270006718983</v>
+        <v>-2.286627927788189</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.982592367487022</v>
+        <v>-1.964595278325497</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.001043</t>
+          <t>X &lt; 0.001045</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.390902487795422</v>
+        <v>-1.3783801981198</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3563901029647454</v>
+        <v>-0.3434802933886942</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.659284942032265</v>
+        <v>-1.675407135696105</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.749660601482127</v>
+        <v>-1.736681459083663</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.100101702367937</v>
+        <v>-1.116669853878207</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3611586608995196</v>
+        <v>-0.3481157646051543</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.465080976667863</v>
+        <v>-1.481391245284122</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.048774590800001</v>
+        <v>-1.035593581504763</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.295346991175805</v>
+        <v>-2.311374191920414</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.236722493066324</v>
+        <v>-1.25361400987687</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.466455393446559</v>
+        <v>-1.483297683430457</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.266143032561295</v>
+        <v>-1.252690743841185</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.655972698234365</v>
+        <v>-1.672841597154594</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.375792727502123</v>
+        <v>-1.361340658546105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001873</t>
+          <t>X &lt; 0.001875</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.592318008471054</v>
+        <v>-1.579795718795431</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8658497315181251</v>
+        <v>-0.8529399219420739</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.014500522811751</v>
+        <v>-2.027058603336179</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.907413952799601</v>
+        <v>-1.920001191275574</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.298292624674517</v>
+        <v>-1.311320170420281</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.9032897113490961</v>
+        <v>-0.8902468150547307</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.157029130391429</v>
+        <v>-1.170079125540411</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9409524022817592</v>
+        <v>-0.9277713929865214</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.805555036755912</v>
+        <v>-1.818426560734288</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.115173153513204</v>
+        <v>-1.128603219131008</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.29306505269966</v>
+        <v>-1.306469184120566</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.307557750681703</v>
+        <v>-1.294105461961593</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.603149055324359</v>
+        <v>-1.616504604620062</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.375413474176071</v>
+        <v>-1.363857358746223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002704</t>
+          <t>X &lt; 0.002706</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.700467895863639</v>
+        <v>-1.709707804313275</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.060415020652798</v>
+        <v>-1.092959021627308</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.290528430418611</v>
+        <v>-2.279415300037748</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.880357120897223</v>
+        <v>-1.869512858761425</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.494566541041841</v>
+        <v>-1.484384507307148</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.982440189414632</v>
+        <v>-0.9494952186975709</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.215959058493141</v>
+        <v>-1.248797852641843</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.7810806016045433</v>
+        <v>-0.7912492888739067</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.5062912985737</v>
+        <v>-1.539221569913643</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.78560082045108</v>
+        <v>-0.8196940159523081</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.095606597176683</v>
+        <v>-1.12957757652098</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9321911817667399</v>
+        <v>-0.9425186987031182</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.242587002712938</v>
+        <v>-1.276685029230627</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.012055646008328</v>
+        <v>-1.027132590757162</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003535</t>
+          <t>X &lt; 0.003536</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.803254271130221</v>
+        <v>-1.790731981454599</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.247321100799851</v>
+        <v>-1.254678810714744</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.19750151467489</v>
+        <v>-2.204556669074357</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.701681249965624</v>
+        <v>-1.708912370904535</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.298217693049622</v>
+        <v>-1.305686478321213</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8855683820620754</v>
+        <v>-0.8725254857677101</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.141748492571978</v>
+        <v>-1.149248133820358</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4948327749493231</v>
+        <v>-0.4816517656540853</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.9575745169634402</v>
+        <v>-0.9652232421922378</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5949869187273222</v>
+        <v>-0.6029033368289305</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7014792191783386</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.5901729849098345</v>
+        <v>-0.5767206961897244</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.9505376973730648</v>
+        <v>-0.9584100110415932</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8333360971782611</v>
+        <v>-0.8266750119530712</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004365</t>
+          <t>X &lt; 0.004367</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.342007754962239</v>
+        <v>-1.329485465286616</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.085814725495354</v>
+        <v>-1.091404286891972</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.985914159323897</v>
+        <v>-1.991236510098418</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.208607597977156</v>
+        <v>-1.214190264206202</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8199984077700861</v>
+        <v>-0.8257796922231009</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8370218788594528</v>
+        <v>-0.8239789825650874</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8680074014775343</v>
+        <v>-0.8737487408529176</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3723141103638241</v>
+        <v>-0.3782838210232171</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.86885432190806</v>
+        <v>-0.8746607121368157</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5802969773821687</v>
+        <v>-0.5863019063905384</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6256196569694623</v>
+        <v>-0.6316349953932985</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.641778242397443</v>
+        <v>-0.6477877110789265</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9024523836763692</v>
+        <v>-0.9084207845817787</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.7383085491695169</v>
+        <v>-0.7332132265027838</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005196</t>
+          <t>X &lt; 0.005197</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6619958566767465</v>
+        <v>-0.6494735670011238</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7003426724738446</v>
+        <v>-0.7047439388331895</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.207632829196712</v>
+        <v>-1.211905933774752</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6058377602457341</v>
+        <v>-0.6102974079046604</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.47766897540005</v>
+        <v>-0.4822189042330294</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3573600312730747</v>
+        <v>-0.3619261082838818</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3595171825326062</v>
+        <v>-0.3640924293098138</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.100633994163239</v>
+        <v>0.09586659232019201</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3973944399895828</v>
+        <v>-0.4020079587823062</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2218934451258434</v>
+        <v>-0.2266396842350105</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.2784022961014117</v>
+        <v>-0.2831504640296956</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.09567821487830486</v>
+        <v>-0.1004855492228742</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5302028092518114</v>
+        <v>-0.5349076838307454</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1971045007579377</v>
+        <v>-0.193286641472902</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.006027</t>
+          <t>X &lt; 0.006028</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3281</v>
+        <v>3282</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3987206517218169</v>
+        <v>-0.3861983620461942</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5975719088802691</v>
+        <v>-0.6009060094512506</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.158446860912981</v>
+        <v>-1.161638160645964</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7081264436567878</v>
+        <v>-0.7114478787381273</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.561544162964978</v>
+        <v>-0.5649470336308369</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6428354254441189</v>
+        <v>-0.6461961070704518</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6199147110378505</v>
+        <v>-0.6232897537245279</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2492291028857494</v>
+        <v>-0.2527492173124415</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.567406927352387</v>
+        <v>-0.5708361521516281</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4267692153150477</v>
+        <v>-0.4302986219764122</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4318736724716956</v>
+        <v>-0.4354168440959185</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3195598027827913</v>
+        <v>-0.3231368865766768</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7837131159409907</v>
+        <v>-0.7871782577202922</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5474387325724237</v>
+        <v>-0.5444214193628554</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3295606514275207</v>
+        <v>-0.3170383617518979</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5407983689606652</v>
+        <v>-0.5433427467949485</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.006809046237329</v>
+        <v>-1.009240030719738</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7167253991644742</v>
+        <v>-0.7192349698456937</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.604178127203717</v>
+        <v>-0.6067484867314761</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5221930312693246</v>
+        <v>-0.5247735935980842</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4756873226013596</v>
+        <v>-0.4782869605803413</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1755334409031875</v>
+        <v>-0.178244625382419</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2784688417009633</v>
+        <v>-0.2811547673732733</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2448957175171316</v>
+        <v>-0.2476353999436114</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1441430368421663</v>
+        <v>-0.1469235965479783</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1224561865128564</v>
+        <v>-0.1252427759618087</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5264625163482606</v>
+        <v>-0.5291547511061552</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2604834918526393</v>
+        <v>-0.2582188799901601</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.007688</t>
+          <t>X &lt; 0.007689</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4500688456478343</v>
+        <v>-0.4520110833414606</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4898840132632216</v>
+        <v>-0.4918797160363226</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9254717385190858</v>
+        <v>-0.9273629410562236</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5577187703797932</v>
+        <v>-0.55970817004998</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5523570996359908</v>
+        <v>-0.554370305172732</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4903395239407615</v>
+        <v>-0.4923593237946235</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.420765174585199</v>
+        <v>-0.4228087686497588</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1764514771752843</v>
+        <v>-0.1785826573602449</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.08281606872861147</v>
+        <v>-0.08497685838609925</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1093234422409139</v>
+        <v>-0.1115116067389792</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.04756873044767218</v>
+        <v>-0.04978335244694421</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.109049813602617</v>
+        <v>-0.1112470842148596</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3741761206911249</v>
+        <v>-0.3763172571697027</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3319631317103102</v>
+        <v>-0.3301424436387919</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5128400987063344</v>
+        <v>-0.5143212029481461</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6009688064896039</v>
+        <v>-0.6024766857108119</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.9814120498543986</v>
+        <v>-0.9828303816685917</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7018820918450857</v>
+        <v>-0.7033725491811467</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.7132820645608291</v>
+        <v>-0.714786893049336</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6440660397815634</v>
+        <v>-0.6455811528599469</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4713189093494563</v>
+        <v>-0.472884069402042</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.383906189990455</v>
+        <v>-0.3855102327088744</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1870668599398186</v>
+        <v>-0.1887267756629214</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2659774428805477</v>
+        <v>-0.2676432500181249</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2124741685683134</v>
+        <v>-0.2141616420454469</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1629380576749</v>
+        <v>-0.1646387225027723</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4058255204497456</v>
+        <v>-0.4074744601060374</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3842657759968091</v>
+        <v>-0.3828084927010167</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2534592790782</v>
+        <v>-0.2546195402252849</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1741943231113368</v>
+        <v>-0.1754136247771143</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5811388311207608</v>
+        <v>-0.5822613490240869</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.541625409627926</v>
+        <v>-0.5427558352759974</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.593860419062139</v>
+        <v>-0.5949903562454466</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4395679597559266</v>
+        <v>-0.440731997325905</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2214491346968614</v>
+        <v>-0.2226729883101015</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2543874176339784</v>
+        <v>-0.2556142111419248</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1434502766482737</v>
+        <v>-0.1447082499008872</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3488590558174494</v>
+        <v>-0.3500836971107901</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1712312953133903</v>
+        <v>-0.1725080276012818</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2272035843681763</v>
+        <v>-0.228465457863571</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.291080582815205</v>
+        <v>-0.2923362004591112</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2894209768357499</v>
+        <v>-0.2883197666575796</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1794521274204115</v>
+        <v>-0.1803025336018393</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2175439024836976</v>
+        <v>-0.2184125301438229</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.521881151410625</v>
+        <v>-0.5226791349516873</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4545814477979206</v>
+        <v>-0.4553948472411946</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.492896431475323</v>
+        <v>-0.4937096681164377</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4887429852366765</v>
+        <v>-0.4895526263877343</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3291433186935109</v>
+        <v>-0.3299957016646999</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3213353759834447</v>
+        <v>-0.3221982049787613</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.112071058085661</v>
+        <v>-0.1129889822273853</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2817473828550874</v>
+        <v>-0.2826368751328019</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1902197787981663</v>
+        <v>-0.1911366989570666</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1158140105508565</v>
+        <v>-0.1167498800281876</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.213901859472621</v>
+        <v>-0.2148202674518558</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1549320993127523</v>
+        <v>-0.1541433765390181</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3959</v>
+        <v>3960</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1520485921132959</v>
+        <v>-0.1527005762177112</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1387565818773311</v>
+        <v>-0.139433442832825</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3437093551360633</v>
+        <v>-0.3443401414431264</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3257877490378576</v>
+        <v>-0.3264216645129636</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3717583996548441</v>
+        <v>-0.3723881572155534</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2622326983085941</v>
+        <v>-0.2628864688706258</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1315482678032041</v>
+        <v>-0.1322364355430636</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1309980493756271</v>
+        <v>-0.13169286606405</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.02370123847113348</v>
+        <v>0.02296625106392014</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1059477353468026</v>
+        <v>-0.1066616039695631</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0694169351725975</v>
+        <v>-0.07014308465210917</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.02084317309074635</v>
+        <v>-0.02158148910705648</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.02285960828675115</v>
+        <v>-0.0236033382899592</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.061938120885074</v>
+        <v>-0.06134568948639441</v>
       </c>
     </row>
     <row r="33">
@@ -5315,46 +5315,46 @@
         <v>3993</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.09703292829784971</v>
+        <v>-0.1094731947879666</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.07255250745638619</v>
+        <v>-0.08461148689405462</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2791014189915941</v>
+        <v>-0.2910693125490198</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.360134626823573</v>
+        <v>-0.3721367484770681</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4102975977977152</v>
+        <v>-0.4221742996696491</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3241783916180552</v>
+        <v>-0.3361292468857968</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2203405017921156</v>
+        <v>-0.2322742474916382</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1487704622140171</v>
+        <v>-0.160595704481679</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.004090020147543783</v>
+        <v>-0.00772374715082691</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1316925044333246</v>
+        <v>-0.1433061408535536</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1472711649702916</v>
+        <v>-0.1588388962850971</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0988376619099256</v>
+        <v>-0.1104166623012119</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1044339900614233</v>
+        <v>-0.1159155000443306</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1410738298964347</v>
+        <v>-0.1515034655945868</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.02757008315137455</v>
+        <v>0.02711460944587429</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.08770661797027657</v>
+        <v>-0.08814760061251548</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1724820245383754</v>
+        <v>-0.1729056467957406</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2266643609847421</v>
+        <v>-0.2270736862287492</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3063663867580075</v>
+        <v>-0.3067608216448647</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2676223747202755</v>
+        <v>-0.2680240564590193</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1903900067426036</v>
+        <v>-0.1908117382117496</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.09938946135597604</v>
+        <v>-0.09983794078331698</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.05136477193651245</v>
+        <v>0.05087822033452483</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.06671312833573495</v>
+        <v>-0.06717796993586234</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.08415056171092772</v>
+        <v>-0.08461307274047414</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.08540699501372728</v>
+        <v>-0.08586912952051762</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1199009187638467</v>
+        <v>-0.1203583477111181</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1537044134573335</v>
+        <v>-0.1532914234747551</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01673405341252732</v>
+        <v>-0.0170768542656603</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.143765918948084</v>
+        <v>-0.1440883913765063</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2064557133723994</v>
+        <v>-0.2067655858611914</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2346581820099516</v>
+        <v>-0.2349604354223729</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2443275636689748</v>
+        <v>-0.244631169394296</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2035358294498621</v>
+        <v>-0.2038476388391146</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1521184978628369</v>
+        <v>-0.1524436557901865</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.00819582430970911</v>
+        <v>0.007828032100796634</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1081715449394167</v>
+        <v>0.1077786122332398</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.01564946330510253</v>
+        <v>-0.0160177999049651</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.009965717930327855</v>
+        <v>-0.01033699059468773</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.03551163937068935</v>
+        <v>-0.03587658454915044</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.02384089185534322</v>
+        <v>-0.02421167925289325</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.05538882578868254</v>
+        <v>-0.05508534874498849</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/hash_rate_ma_ratio_30.xlsx
@@ -568,1249 +568,1249 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01017</t>
+          <t>X ≈ -0.01014</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.88919907301814</v>
+        <v>15.86023644671014</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.039289545216015</v>
+        <v>9.038177182382945</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.64835249410973</v>
+        <v>8.648258569358156</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.529695474970765</v>
+        <v>3.529224046447361</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.993416530898344</v>
+        <v>3.04186857767349</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.214604857179907</v>
+        <v>-7.190735960338436</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.30080936589443</v>
+        <v>-7.252919063330459</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.02428526824142</v>
+        <v>-12.97516730461594</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.08848499404926</v>
+        <v>-13.01536650154898</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.683013603411254</v>
+        <v>-8.583791283075058</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-14.149018803397</v>
+        <v>-14.04921596878366</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-19.37876882908612</v>
+        <v>-19.25516140313192</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.018097199553715</v>
+        <v>-3.869448252519305</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.056561000488777</v>
+        <v>-8.884562240922115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.009337</t>
+          <t>X ≈ -0.009312</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.646746668728049</v>
+        <v>4.617689745377398</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.041833781613164</v>
+        <v>3.040674484143047</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.348118675310978</v>
+        <v>8.348024133918372</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.779572507414123</v>
+        <v>2.779096596216853</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.944629732365392</v>
+        <v>7.993111057860737</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.09494590734505</v>
+        <v>11.11891271368765</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.161110575999224</v>
+        <v>8.209072408627847</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.5497484294582</v>
+        <v>10.59896018288222</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.637787474403623</v>
+        <v>7.710974038946134</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.4989938322415</v>
+        <v>12.59827183934625</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.29751455732915</v>
+        <v>12.3973696203837</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.943720795349947</v>
+        <v>-1.820091169556804</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4920708453849727</v>
+        <v>0.6407222822853882</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.139267767408469</v>
+        <v>-1.967269007844408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.008507</t>
+          <t>X ≈ -0.008483</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-10.58605069945074</v>
+        <v>-9.002690926364906</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.238952989452137</v>
+        <v>-4.080875591259733</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10.27180824626711</v>
+        <v>-8.809937483058029</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.8658582017874252</v>
+        <v>-2.177519083759549</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.9170305692686824</v>
+        <v>-0.49735096394582</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.21410177198797</v>
+        <v>-0.2251708562273791</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.512922836363316</v>
+        <v>-4.625760819570893</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.658009136702063</v>
+        <v>-2.921324968558238</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.687339149486512</v>
+        <v>-9.4725766044442</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.215596444349011</v>
+        <v>-8.12647487749723</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.0696256688201</v>
+        <v>-12.67706724671829</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.389459400510226</v>
+        <v>-8.276449963608144</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.161495026939008</v>
+        <v>-4.326974883710385</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.26219135544833</v>
+        <v>-6.252983293554117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.007676</t>
+          <t>X ≈ -0.007653</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.404060904781751</v>
+        <v>-4.495160741595349</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.8076614254641683</v>
+        <v>1.901148191071435</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-9.361674579419571</v>
+        <v>-8.462475590803294</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.411602893774145</v>
+        <v>1.638988843171575</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.007080478967502302</v>
+        <v>3.146501574529999</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-15.35039797323735</v>
+        <v>-12.54787848723431</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-17.39585057243254</v>
+        <v>-16.60420104125411</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-13.95101415698013</v>
+        <v>-13.07959860683308</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-14.01542447287204</v>
+        <v>-13.11980561872394</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-16.82712832650589</v>
+        <v>-15.94439483387318</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-9.198824342388335</v>
+        <v>-8.158542662793906</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-9.166844357765164</v>
+        <v>-8.102519569260927</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-11.5496665652316</v>
+        <v>-10.49928828997668</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.366158523711881</v>
+        <v>-8.252983293556092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006846</t>
+          <t>X ≈ -0.006823</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.306149295895132</v>
+        <v>0.1922079722800092</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.030717299282422</v>
+        <v>-1.386090175279918</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.057936187482603</v>
+        <v>-0.4305618660607919</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.803367539732058</v>
+        <v>2.393662442608424</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.266557054677577</v>
+        <v>0.5577252488018729</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.931140524587839</v>
+        <v>2.1791285199645</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1129090745566117</v>
+        <v>0.7706058645516762</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.38197963178586</v>
+        <v>1.65487285658277</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.057869180145474</v>
+        <v>4.317581064762166</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.946713900964205</v>
+        <v>6.195314012313631</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.112642106196148</v>
+        <v>8.693410038961986</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.065860267479529</v>
+        <v>0.649834066431211</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.252911194500591</v>
+        <v>1.605766272523717</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.630461505176307</v>
+        <v>-2.198929239502654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.006015</t>
+          <t>X ≈ -0.005994</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.556312509027052</v>
+        <v>6.218725070867471</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>13.99449908467915</v>
+        <v>10.87240258340936</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.938397706860172</v>
+        <v>-0.7336339208430189</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.994899574546217</v>
+        <v>-8.085562978386378</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.540001046967987</v>
+        <v>-7.328920169232013</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.947338707126598</v>
+        <v>-7.058206204684282</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.037683725496031</v>
+        <v>-7.120181777865938</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.49208673201364</v>
+        <v>-2.595198242443971</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.554227898197766</v>
+        <v>-3.881209658072059</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-7.999438620607549</v>
+        <v>-7.202886779059114</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.015544109791726</v>
+        <v>-3.66189279088573</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.9121070818958188</v>
+        <v>1.39268139827621</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.104606531132326</v>
+        <v>-0.251862290968127</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7178750897337949</v>
+        <v>2.497016706443908</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005184</t>
+          <t>X ≈ -0.005164</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.400920772802777</v>
+        <v>-5.490867809969608</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.992384865838709</v>
+        <v>-7.070657262229268</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.522494668323361</v>
+        <v>-4.472271071778827</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.861147943213972</v>
+        <v>-5.341975039701737</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.399541153557259</v>
+        <v>-5.831732518717466</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2275424547320881</v>
+        <v>0.4262469464768373</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6574655650660191</v>
+        <v>1.364338478197382</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.037524640187861</v>
+        <v>3.894440647352447</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.069270042963083</v>
+        <v>1.861260295813175</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.160169648333088</v>
+        <v>3.036354926995372</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.83656431275201</v>
+        <v>6.829692070808996</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>8.813472834506264</v>
+        <v>7.889122022197647</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.542605080749617</v>
+        <v>2.497397332230086</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.827445131343261</v>
+        <v>0.7470167064439011</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.004354</t>
+          <t>X ≈ -0.004335</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-11.84519445449187</v>
+        <v>-11.19035172381441</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-5.454476001520433</v>
+        <v>-6.717064535199107</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.966025967775309</v>
+        <v>-4.516815888555726</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.615146145076693</v>
+        <v>-6.121026615282716</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-10.7231166085927</v>
+        <v>-10.08527300100499</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6223036481673887</v>
+        <v>-1.135285330129093</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.167869494500714</v>
+        <v>-5.925751378794345</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.962381425291859</v>
+        <v>-3.788585503009934</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.701486451588941</v>
+        <v>-6.431534819242103</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.20617882125309</v>
+        <v>-2.045055023452505</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.411015988359836</v>
+        <v>-2.249927294918514</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.8727481268870676</v>
+        <v>-2.192409711044</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.863541016523499</v>
+        <v>-6.065448129523823</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.424982053122555</v>
+        <v>-7.557331119643045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.003523</t>
+          <t>X ≈ -0.003506</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.440215585810861</v>
+        <v>-4.7558728487626</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.393008069547733</v>
+        <v>-5.70623403087852</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.818232163923135</v>
+        <v>-3.547704609077599</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.626836945811654</v>
+        <v>-7.255026691026245</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.54011516109523</v>
+        <v>-6.469539960125495</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.55898914916083</v>
+        <v>-7.476237770312721</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.674228729167218</v>
+        <v>-4.339620349017729</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.797896249320956</v>
+        <v>-5.729964503354886</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4.546152067964194</v>
+        <v>-5.128315259392757</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.739839344164956</v>
+        <v>-5.313007583533128</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.918625898663485</v>
+        <v>-7.440280433311003</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.25416582554093</v>
+        <v>-4.821743269723243</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.360110155801443</v>
+        <v>-3.936610754150372</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.451297842596595</v>
+        <v>-5.611957652530307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.002693</t>
+          <t>X ≈ -0.002677</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>183</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.109264683589615</v>
+        <v>-0.8833860593144038</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.007587250647901556</v>
+        <v>0.798708902517042</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.565554030281696</v>
+        <v>-2.322815091303809</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.706250472792142</v>
+        <v>-5.706717583048565</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.388185612579655</v>
+        <v>1.982022345248801</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.139322564181732</v>
+        <v>1.708790661223674</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.601011612199237</v>
+        <v>1.103358225521959</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.225553607132881</v>
+        <v>2.274365695745971</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.655074292342</v>
+        <v>-1.035390287657528</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.413440696847637</v>
+        <v>-0.2219318002730262</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.618777626841023</v>
+        <v>-0.4263440405752306</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.038309047875927</v>
+        <v>0.1775762280254654</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.551356468757753</v>
+        <v>-0.7638555655937864</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.326621397385047</v>
+        <v>-0.5152783755234296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.001862</t>
+          <t>X ≈ -0.001847</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3559244008626834</v>
+        <v>0.4639296821681214</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.829039331761557</v>
+        <v>3.196077751452052</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2357565356466935</v>
+        <v>0.6493949792623255</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9614290364580427</v>
+        <v>2.396799012767602</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.17845659466311</v>
+        <v>0.8294907965206235</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.54927369000027</v>
+        <v>-1.596066699593983</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.637067530656466</v>
+        <v>-1.655927195184404</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.434736994436179</v>
+        <v>0.03656317784722773</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.032775871839021</v>
+        <v>-1.079222329607354</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.886164078006537</v>
+        <v>-2.443042107947811</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.25230729854075</v>
+        <v>-1.568205461205828</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.683563372571825</v>
+        <v>-0.9706491436484583</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.104287935147255</v>
+        <v>-1.906532540234984</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2595099254868742</v>
+        <v>0.5037734632006661</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.001032</t>
+          <t>X ≈ -0.001017</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.979720090129511</v>
+        <v>2.151770648666627</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.488286731878645</v>
+        <v>3.673869841229049</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.769689095022322</v>
+        <v>5.500631390275665</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.454514304443514</v>
+        <v>4.744057542329003</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.027195970370336</v>
+        <v>2.926397658583689</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.433701397759492</v>
+        <v>2.312167829201115</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.013135187787555</v>
+        <v>1.808926072135222</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6828062445323937</v>
+        <v>-1.317679178977677</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.1897197547639</v>
+        <v>-0.9108005379685764</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.082609945152612</v>
+        <v>1.371978738762834</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4604233597789857</v>
+        <v>-0.6079435576941634</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.318337063577466</v>
+        <v>-1.438625909331861</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.631554705995299</v>
+        <v>-2.722927209250457</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.407124910265615</v>
+        <v>-2.475205515778313</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.0002012</t>
+          <t>X ≈ -0.0001881</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.346165176088277</v>
+        <v>-1.356996534870767</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.347091271011415</v>
+        <v>-4.078544660300231</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.517556391262026</v>
+        <v>-4.470409867429041</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.003469419846439</v>
+        <v>-3.579446061353202</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-5.313607214875525</v>
+        <v>-4.450380654021913</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.943132652989242</v>
+        <v>-0.7533013266388906</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.185899393625952</v>
+        <v>-2.716700466663688</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.654686698211513</v>
+        <v>-2.800999463071584</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.64438711416161</v>
+        <v>-5.504910021893416</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.585865875443027</v>
+        <v>-3.663457817646979</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.713257908330455</v>
+        <v>-6.15666946574499</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.140899112220872</v>
+        <v>-4.575809928423205</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.642937734030852</v>
+        <v>-3.065203102381773</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2711358992766009</v>
+        <v>-0.9094718431744155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0006295</t>
+          <t>X ≈ 0.0006413</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7776580714952033</v>
+        <v>-2.252697156090179</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.520544451836543</v>
+        <v>0.5407902169166192</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.589984832075437</v>
+        <v>2.581984178146065</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.720334948351613</v>
+        <v>1.739446449009215</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>6.587182573574992</v>
+        <v>5.62847797411424</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.648837997336784</v>
+        <v>6.874477861457869</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.118722909596585</v>
+        <v>3.896373385758167</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>6.611000484169274</v>
+        <v>5.86413315644878</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.592628688169469</v>
+        <v>3.883874427459261</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.722717279409935</v>
+        <v>4.03478576546248</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.518150068138993</v>
+        <v>4.806565362218322</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.062457553214472</v>
+        <v>4.378496627226461</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.153203865278165</v>
+        <v>3.009624739798404</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.378939515504698</v>
+        <v>3.259211828395124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.00146</t>
+          <t>X ≈ 0.001471</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.11622907968858</v>
+        <v>-2.089760517292049</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.731431150237938</v>
+        <v>-3.254528148355128</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.712783538797318</v>
+        <v>-4.492145584546165</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.323729948257125</v>
+        <v>-3.521214559896094</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.788776585247312</v>
+        <v>-3.355374633671751</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.009975779803185</v>
+        <v>-6.452902165829812</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.200263227259285</v>
+        <v>0.6420762943602085</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1062224547266979</v>
+        <v>-1.506359974385504</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.932624700381844</v>
+        <v>0.9837922271968154</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1771997676184114</v>
+        <v>-1.104035196720076</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.03822969066507653</v>
+        <v>-1.308849627557258</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.607347415533567</v>
+        <v>-2.938311378882666</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.188532829399804</v>
+        <v>-2.069891418211007</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.382965246400062</v>
+        <v>-2.244544474990697</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002291</t>
+          <t>X ≈ 0.0023</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.664707836586942</v>
+        <v>-3.612135424179591</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.853871504321333</v>
+        <v>-3.418684961548045</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.119650932868637</v>
+        <v>-4.541636652696162</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.493840045276883</v>
+        <v>-1.550232087183502</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.745320924172333</v>
+        <v>-2.753951196637587</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.379288772009744</v>
+        <v>-1.405006080239758</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.821582867414982</v>
+        <v>-1.82694384463602</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.208871536662592</v>
+        <v>0.9247229415305185</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5048618922854402</v>
+        <v>1.236163759565592</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.439757456071163</v>
+        <v>2.049203872929247</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.164396517311765</v>
+        <v>0.7682760132608095</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.626563748058587</v>
+        <v>2.108506588063982</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.206425153793653</v>
+        <v>1.711065003758293</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.432160804020107</v>
+        <v>2.169955774544263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003121</t>
+          <t>X ≈ 0.003129</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.46875047347671</v>
+        <v>-2.308969614464985</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.6241888053518</v>
+        <v>-2.431911227859516</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.558439384723464</v>
+        <v>-1.727880004841289</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3365990990240704</v>
+        <v>-0.5031814527218685</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.2179937779106211</v>
+        <v>0.1036473810168914</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2148397914826603</v>
+        <v>0.008073818375791575</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2998584371485364</v>
+        <v>-0.4172276772460108</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.148879883092249</v>
+        <v>2.407075919482736</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.912788432395651</v>
+        <v>4.201287318772906</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.239157329475482</v>
+        <v>1.548171816605524</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.858450769107641</v>
+        <v>3.174771634519772</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.527959429059045</v>
+        <v>2.866732833265317</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.743442880592362</v>
+        <v>2.106030452487154</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8742880198699012</v>
+        <v>1.256174215601412</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.003952</t>
+          <t>X ≈ 0.003959</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.334609904904177</v>
+        <v>3.766370654658168</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5469642586323005</v>
+        <v>0.6506875040676618</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1390647438871397</v>
+        <v>0.8521996826469334</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.788539931790538</v>
+        <v>4.423531949045213</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.031802950612139</v>
+        <v>4.699081320549766</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3483684036783501</v>
+        <v>-0.1629441548648032</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.903768894813631</v>
+        <v>2.071413627025073</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6604808369894855</v>
+        <v>0.4571806397024361</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.03441963647716761</v>
+        <v>-0.3440162247465466</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4256292339505663</v>
+        <v>-0.7849970395814836</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1496611509592967</v>
+        <v>-0.2249106766182152</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.377705622587506</v>
+        <v>-1.698275013147743</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4007177033493292</v>
+        <v>-0.9464726000158592</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2156429468772885</v>
+        <v>-0.3142859755484366</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.004782</t>
+          <t>X ≈ 0.004789</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>8.268750239356528</v>
+        <v>8.508947383770625</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.363343000424962</v>
+        <v>4.427134850670612</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>9.00417870594049</v>
+        <v>8.634454577304325</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.30768225025389</v>
+        <v>6.46209057565212</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.018514908054016</v>
+        <v>3.214484726376419</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.692743621118765</v>
+        <v>5.325458390164293</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.326900064434973</v>
+        <v>5.725208929877404</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.318547016978506</v>
+        <v>5.717204020343523</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.798849264125458</v>
+        <v>5.226691871260165</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.49021487146527</v>
+        <v>3.943176581013098</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.285513713205177</v>
+        <v>3.741172121358296</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.072185443542104</v>
+        <v>6.561818012938048</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.35845660857732</v>
+        <v>3.866635438898484</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.877770240455284</v>
+        <v>6.880657259439303</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.005613</t>
+          <t>X ≈ 0.005618</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>209</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.498186673695336</v>
+        <v>3.465473799763821</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9318213213778392</v>
+        <v>0.9353876488689252</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4198878624201541</v>
+        <v>-0.883677739664293</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.203538316917992</v>
+        <v>-2.189368947153852</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.784890070970626</v>
+        <v>-1.24784651837917</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.836798337986288</v>
+        <v>-4.314061737697529</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.443039797730876</v>
+        <v>-3.89693998297367</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.388577341039138</v>
+        <v>-4.842472058897293</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.057214999954262</v>
+        <v>-2.494972088279397</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-3.428664896762591</v>
+        <v>-3.318158845287833</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.676428255979772</v>
+        <v>-2.571654966554568</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.59898790266746</v>
+        <v>-2.99194122919031</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.497607655502399</v>
+        <v>-3.870449208202984</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.707278703840572</v>
+        <v>-5.535279944273796</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.006443</t>
+          <t>X ≈ 0.006448</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.008312279501745</v>
+        <v>1.290205760609808</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.5590606670994589</v>
+        <v>0.8721876805855189</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.908475328856085</v>
+        <v>2.231539478737474</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8682762717415713</v>
+        <v>0.01971246456714226</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.406565824837266</v>
+        <v>-1.641945801139421</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.797784948983839</v>
+        <v>2.149102823318124</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.294469938554876</v>
+        <v>2.674306052678411</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.246005945930932</v>
+        <v>1.624685436458741</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.254791231268612</v>
+        <v>5.692849070666554</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.242081737264343</v>
+        <v>4.280094865452739</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.362961974352984</v>
+        <v>6.18284049164081</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.653154080196678</v>
+        <v>3.890779940858636</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.395793924557687</v>
+        <v>4.674442432663838</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.202924923621495</v>
+        <v>5.51172258879685</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.007274</t>
+          <t>X ≈ 0.007277</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>131</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.039942173108315</v>
+        <v>-4.058450937751637</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.8697299374706091</v>
+        <v>0.4368424183971413</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.238317331341484</v>
+        <v>0.7916971740352707</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.65861881080766</v>
+        <v>3.215158736004476</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.8302529218341093</v>
+        <v>0.4398793304394744</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3642681728432393</v>
+        <v>-0.04682948689881528</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.042916592203028</v>
+        <v>0.6536859280643199</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1875108302097104</v>
+        <v>-0.5682868324132073</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.095018463649275</v>
+        <v>4.728002648023484</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.481740888693416</v>
+        <v>3.136434463454094</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.513680951807316</v>
+        <v>2.934484428482257</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2579827682847409</v>
+        <v>0.7025748299692367</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.654625808101095</v>
+        <v>3.803315355878922</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.226508770680006</v>
+        <v>-2.054510011113344</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.008104</t>
+          <t>X ≈ 0.008107</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>114</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.497994497891142</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.076090123339029</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.732487543440932</v>
+        <v>-2.71346030887976</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.233841347221002</v>
+        <v>-5.214023715908219</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.772130900316697</v>
+        <v>-5.702100212312075</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.47475687068161</v>
+        <v>-5.430096456525106</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.050695300123159</v>
+        <v>-1.989743385682253</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.903728856190554</v>
+        <v>-6.83418288524706</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.455939082888861</v>
+        <v>-3.382681973109165</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.183050861674822</v>
+        <v>-5.083703536380249</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.387752019935114</v>
+        <v>-5.287843983916439</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.844601937755172</v>
+        <v>-1.720905316726927</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.387559808612494</v>
+        <v>-1.238870260834666</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.039017140842049</v>
+        <v>-1.867018381275386</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.008935</t>
+          <t>X ≈ 0.008936</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>106</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.839838686446775</v>
+        <v>8.274242825305024</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>14.77582240470366</v>
+        <v>15.15449870057662</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.43765479353352</v>
+        <v>12.84683518212337</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.077313899386063</v>
+        <v>5.448333850153851</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.595628119875272</v>
+        <v>4.009427003407929</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.723190828755662</v>
+        <v>7.116575521058074</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.52527292231963</v>
+        <v>8.95106052383462</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.284619372872513</v>
+        <v>4.713730017583849</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.393448537104454</v>
+        <v>1.466705646884151</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.230055164885805</v>
+        <v>-3.130707839591231</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.282224808929556</v>
+        <v>1.382132844948231</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.456981944375521</v>
+        <v>-2.333285323347276</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.72664078721678</v>
+        <v>3.875330334994608</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.008980211028188</v>
+        <v>3.18097897059485</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>94</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.838232905635898</v>
+        <v>2.809037111283267</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.964442549130091</v>
+        <v>-1.965629335574747</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.89610521505103</v>
+        <v>1.895951825046708</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.090160145873469</v>
+        <v>3.089665653495466</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.615700380011823</v>
+        <v>3.664246299777595</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.469904313757375</v>
+        <v>-2.445946904807762</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.021683316810282</v>
+        <v>-2.972435754416566</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.172653675603101</v>
+        <v>1.245910785382797</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.450394453741367</v>
+        <v>2.549741779035941</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9457960662209857</v>
+        <v>-0.8458880302023104</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.407731022304574</v>
+        <v>4.531427643332819</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.923750381757124</v>
+        <v>3.072439929534951</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.277145606451711</v>
+        <v>5.449144366018373</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>61</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.617444625203326</v>
+        <v>1.588248830850695</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.924291319024746</v>
+        <v>4.923104532580091</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.08689698345005</v>
+        <v>11.08674359344573</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.938433602448256</v>
+        <v>7.937939110070253</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.400144049352562</v>
+        <v>7.448689969118334</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>14.25489512816797</v>
+        <v>14.27885253711759</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>12.53084050660672</v>
+        <v>12.57885218559704</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.06377186281998</v>
+        <v>12.1130194252137</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.724101181707077</v>
+        <v>8.797358291486773</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.15287090996735</v>
+        <v>11.25221823526192</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.669481227117004</v>
+        <v>7.769389263135679</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.064515117177237</v>
+        <v>6.188211738205482</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.20174131304415</v>
+        <v>12.35043086082198</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.87009991409036</v>
+        <v>6.042098673657023</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>33</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.094841545223183</v>
+        <v>5.065645750870551</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.513958482462471</v>
+        <v>6.512771696017815</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.119187097707389</v>
+        <v>6.119033707703068</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-5.871799879916374</v>
+        <v>-5.872294372294377</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.410089433012025</v>
+        <v>-6.361543513246254</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-9.143018433680012</v>
+        <v>-9.119061024730399</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-12.25803182324921</v>
+        <v>-12.21002014425889</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.634191376126857</v>
+        <v>-3.58494381373314</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.695173532649676</v>
+        <v>-3.62191642286998</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.545092328979493</v>
+        <v>-4.44574500368492</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.81039954784575</v>
+        <v>-10.71049151182707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-10.77602139549042</v>
+        <v>-10.65232477446218</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-11.19617224880383</v>
+        <v>-11.04748270102601</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.9704365985773</v>
+        <v>-10.79843783901064</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>41</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>13.37274250605102</v>
+        <v>13.34354671169839</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4335655382323225</v>
+        <v>-0.4347523246769782</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.36678502823215</v>
+        <v>11.36663163822783</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.93603456206441</v>
+        <v>13.93554006968641</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.95872061872478</v>
+        <v>11.00726653849055</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.378045867872096</v>
+        <v>6.402003276821709</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.85431111836202</v>
+        <v>3.90232279735234</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.826266864819189</v>
+        <v>5.875514427212906</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.765284708296413</v>
+        <v>5.838541818076109</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.354390302210419</v>
+        <v>7.453737627504992</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.149689143950226</v>
+        <v>7.249597179968902</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.306018515817776</v>
+        <v>2.429715136846021</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5531567277395268</v>
+        <v>-0.4044671799616992</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3274210775129589</v>
+        <v>-0.1554223179462966</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>32</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.605916030534353</v>
+        <v>-5.635111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.217102123598202</v>
+        <v>-7.218288910042858</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.231648364764858</v>
+        <v>-1.232142857142861</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.605062082139447</v>
+        <v>7.653608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.692725752508366</v>
+        <v>4.740737431498687</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.60065710872163</v>
+        <v>13.64990467111534</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.289674952198851</v>
+        <v>7.362932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.439756155869034</v>
+        <v>6.539103481163608</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.360054997608827</v>
+        <v>9.459963033627503</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.269433149964144</v>
+        <v>6.393129770992388</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.09928229665074</v>
+        <v>12.24797184442857</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.3250179468772</v>
+        <v>12.49701670644387</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1249 +2210,1249 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01058</t>
+          <t>X &gt; -0.01056</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0319547711327246</v>
+        <v>0.03267546117658782</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1011298528608648</v>
+        <v>0.1008905959488402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.3083190351837004</v>
+        <v>0.3074936495876628</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1330474154117809</v>
+        <v>0.132702995560841</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1234669901149061</v>
+        <v>0.1217920449791308</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1397949728447401</v>
+        <v>0.1387558218257396</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.2403871814305347</v>
+        <v>0.2384112806661705</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.3270814702147504</v>
+        <v>0.324837318678405</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3288545149598363</v>
+        <v>0.3259403912289116</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2296824457952837</v>
+        <v>0.2263124985612635</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2354236385525184</v>
+        <v>0.2320218571568873</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2345265619601946</v>
+        <v>0.230467353733232</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1970816573588507</v>
+        <v>0.1924299121087714</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1662624131832047</v>
+        <v>0.1610466304076041</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.009752</t>
+          <t>X &gt; -0.009727</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4047</v>
+        <v>4058</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.04249238521415322</v>
+        <v>-0.04143091110658759</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05916666181694552</v>
+        <v>0.05904524229131169</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2691639485220847</v>
+        <v>0.2684412756409813</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1171007109068185</v>
+        <v>0.1168001123753228</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1099930486088709</v>
+        <v>0.1081199271572473</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1743226715772437</v>
+        <v>0.1730733042952224</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.2757918600564651</v>
+        <v>0.273486508989464</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.3897639431652493</v>
+        <v>0.3871093955247886</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3918467192274804</v>
+        <v>0.3884058498200389</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2715260892187885</v>
+        <v>0.2675623684112196</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3029562321766974</v>
+        <v>0.2988881752182166</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3266077609791935</v>
+        <v>0.3217011995637975</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2168712294570341</v>
+        <v>0.211448070099884</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2095620536229816</v>
+        <v>0.2033991608549428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.008922</t>
+          <t>X &gt; -0.008897</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4012</v>
+        <v>4023</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.08340050258404119</v>
+        <v>-0.08196514500590979</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03314638534813952</v>
+        <v>0.03310514200177295</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1986845329095175</v>
+        <v>0.1981491056087421</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.09387376352951549</v>
+        <v>0.09363819914278793</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.04164502170671369</v>
+        <v>0.03952070031791521</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07905302719741769</v>
+        <v>0.07784477351501806</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2070016917967479</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.3011299807972918</v>
+        <v>0.2982665475114743</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3286343746534186</v>
+        <v>0.3246996885922471</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1648557574626111</v>
+        <v>0.1602855025194145</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1983177622414232</v>
+        <v>0.1936316873780939</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.346413717976084</v>
+        <v>0.3403347399364662</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2144704352004325</v>
+        <v>0.2077133951243653</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2300528421913057</v>
+        <v>0.2222839199661593</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.008091</t>
+          <t>X &gt; -0.008068</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3969</v>
+        <v>3977</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.03038482330794068</v>
+        <v>0.02121649591502006</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.0902641160400961</v>
+        <v>0.08068953066911888</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3121214665211482</v>
+        <v>0.3023412059554005</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1042714643379341</v>
+        <v>0.1199075567021382</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.03216112688555484</v>
+        <v>0.04573043040496572</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06675595084921326</v>
+        <v>0.08134960604409969</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2473032172971017</v>
+        <v>0.2603157447517077</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3223552219291719</v>
+        <v>0.3355059766639172</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4263131001605984</v>
+        <v>0.4380199575084305</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2448153051264796</v>
+        <v>0.2561343779231748</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3312282100962065</v>
+        <v>0.342500722069687</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.430223882777014</v>
+        <v>0.4400008441263168</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2510455208320721</v>
+        <v>0.2601639007382417</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2895556137958621</v>
+        <v>0.2971801462226296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007261</t>
+          <t>X &gt; -0.007238</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3918</v>
+        <v>3927</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.10112416280068</v>
+        <v>0.07872066242266129</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.08092586622370845</v>
+        <v>0.05751078531130815</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.4380437733978653</v>
+        <v>0.4139380584733345</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.124003366396046</v>
+        <v>0.1005660582749712</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03248759780025523</v>
+        <v>0.006250278327989633</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2674386588962889</v>
+        <v>0.2421495563022944</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4769614212981708</v>
+        <v>0.4750409393787152</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5081494634616845</v>
+        <v>0.5063119937698062</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6142989644343828</v>
+        <v>0.6106431504831278</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4670381548491065</v>
+        <v>0.4624054399526756</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4552794301515206</v>
+        <v>0.4507391150524143</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.555147435678407</v>
+        <v>0.5487673378032554</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4046535648313707</v>
+        <v>0.3971571804774285</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.415242551267248</v>
+        <v>0.406043953706444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.00643</t>
+          <t>X &gt; -0.006409</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3845</v>
+        <v>3853</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.05926022659369323</v>
+        <v>0.07654104629770586</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1210168808093925</v>
+        <v>0.08523631634784579</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4664459937214716</v>
+        <v>0.4301573666528142</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.092119469216982</v>
+        <v>0.05652527643208316</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.009057930608570075</v>
+        <v>-0.004341247188513364</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2168664258155388</v>
+        <v>0.2049482992789251</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4838732083754564</v>
+        <v>0.4693643745038685</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.4725734940760802</v>
+        <v>0.4842529478709778</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5299346924585961</v>
+        <v>0.5394483916830524</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3440170028422358</v>
+        <v>0.3523002662296761</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.309899072452879</v>
+        <v>0.2924319132955233</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5669376989633435</v>
+        <v>0.5468262690468393</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.3695631078831596</v>
+        <v>0.3739448594778381</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4540816659929732</v>
+        <v>0.4560745834228825</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.0056</t>
+          <t>X &gt; -0.005579</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3768</v>
+        <v>3773</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.07350862312694773</v>
+        <v>-0.05369344136876464</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1624911153949569</v>
+        <v>-0.1434870606372911</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4363663010697536</v>
+        <v>0.4548335667587367</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.236944433752484</v>
+        <v>0.229164306483888</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1633247940038487</v>
+        <v>0.1509638982563573</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3428334627679064</v>
+        <v>0.3589510451885758</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6171428166313149</v>
+        <v>0.6302876960489456</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5740275379744091</v>
+        <v>0.5495474337509663</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6338307963546939</v>
+        <v>0.6331808708721454</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5145175556569015</v>
+        <v>0.512495061783099</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3778553158267783</v>
+        <v>0.3762765929495089</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5598840783460872</v>
+        <v>0.5288913603963437</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.420123368553071</v>
+        <v>0.3872140277883744</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4486909829706676</v>
+        <v>0.4127999028393461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.004769</t>
+          <t>X &gt; -0.00475</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3665</v>
+        <v>3673</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.07621128176161562</v>
+        <v>0.09433744261166055</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.05755774034739147</v>
+        <v>0.04511000447547531</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5757285602368754</v>
+        <v>0.5889774447477834</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3521159248377614</v>
+        <v>0.3808424808967814</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2915581344127958</v>
+        <v>0.313847002448405</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3588631270250744</v>
+        <v>0.3571188670974124</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6160095988717629</v>
+        <v>0.6103026488899914</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4485868281441299</v>
+        <v>0.4584803710338008</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5934896660953086</v>
+        <v>0.5997455475685456</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4401649866130697</v>
+        <v>0.4437812075709573</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1963418024070478</v>
+        <v>0.2005778323217058</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3279278322657291</v>
+        <v>0.3285039206522313</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3323701308023814</v>
+        <v>0.3297628079560369</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4099429127708305</v>
+        <v>0.4037006160545786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.003939</t>
+          <t>X &gt; -0.003921</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3553</v>
+        <v>3558</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4520056646663235</v>
+        <v>0.4590758501830479</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2313116888667253</v>
+        <v>0.2636738246167241</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7504193869009228</v>
+        <v>0.754004491776989</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5717425366673226</v>
+        <v>0.5909928311105688</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6387699473079849</v>
+        <v>0.6499624606825591</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3897921106506175</v>
+        <v>0.4053556525614539</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7983328351390639</v>
+        <v>0.821557908357029</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5561096101269101</v>
+        <v>0.595752033629374</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7919240385075383</v>
+        <v>0.8270072794918804</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4920621176237674</v>
+        <v>0.5242241998609245</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2470099905764513</v>
+        <v>0.2797819047310952</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.365776328585774</v>
+        <v>0.4099837035766356</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4961590552325887</v>
+        <v>0.5364658034057825</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6253979074739178</v>
+        <v>0.6610133337626252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003108</t>
+          <t>X &gt; -0.003091</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6706524244641798</v>
+        <v>0.6982093002228851</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4826779350528483</v>
+        <v>0.5374262130521288</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9546049310718345</v>
+        <v>0.9512609937562075</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9381594967781126</v>
+        <v>0.9507750314201928</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9149212370690236</v>
+        <v>0.9764299438236748</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7003521669550423</v>
+        <v>0.7667691075786109</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.042916592203028</v>
+        <v>1.058225694409487</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8400875256329599</v>
+        <v>0.8858201640730954</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.030497272316332</v>
+        <v>1.100090852703524</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7258901159159947</v>
+        <v>0.7918926767008543</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5672618738944308</v>
+        <v>0.6337882906025101</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5722541902227221</v>
+        <v>0.6498865277491248</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6685062825413652</v>
+        <v>0.741580425092657</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8522893376446703</v>
+        <v>0.9486627969788799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.002277</t>
+          <t>X &gt; -0.002262</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3218</v>
+        <v>3219</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7718720735548672</v>
+        <v>0.788122922712887</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5096952113878785</v>
+        <v>0.5225723043313906</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.154787991956759</v>
+        <v>1.137392066625416</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.316011275656713</v>
+        <v>1.329253176324762</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.8880078185735556</v>
+        <v>0.9192620626615735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.675388965372548</v>
+        <v>0.7132152261505098</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.011179056883172</v>
+        <v>1.055659912118841</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7612993674867568</v>
+        <v>0.8068814153013903</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.183219334570047</v>
+        <v>1.221492856023211</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8475487668593615</v>
+        <v>0.8495285509742985</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6915767367392363</v>
+        <v>0.694056764229579</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6638430878523209</v>
+        <v>0.6767373462795447</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8516122127737304</v>
+        <v>0.8271643910123956</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.033066424192349</v>
+        <v>1.031887784418437</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.001447</t>
+          <t>X &gt; -0.001432</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3031</v>
+        <v>3034</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8414523905182847</v>
+        <v>0.80789080323391</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3666013972968543</v>
+        <v>0.3595536795069521</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.240578762877853</v>
+        <v>1.167147986586578</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.337887514102825</v>
+        <v>1.264158918005066</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.01550001430936</v>
+        <v>0.9247359203531005</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9360329497191984</v>
+        <v>0.8540250996715173</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.297956395012477</v>
+        <v>1.221000589393427</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.896785609545347</v>
+        <v>0.8538520395363989</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.381632763668854</v>
+        <v>1.361780367342149</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.077903204995266</v>
+        <v>1.050295054567115</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.8732020467350736</v>
+        <v>0.8319995828536833</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8086682307422279</v>
+        <v>0.7771877420068591</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.033978866571559</v>
+        <v>0.9938532282835695</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.080791618932672</v>
+        <v>1.064089877175611</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0006164</t>
+          <t>X &gt; -0.0006029</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2807</v>
+        <v>2809</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.750618060374741</v>
+        <v>0.7002464581921259</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1174893506469274</v>
+        <v>0.09407801685566852</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8791534994648345</v>
+        <v>0.8200373543936195</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.009378643053196</v>
+        <v>0.9854201531517788</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7751651749229538</v>
+        <v>0.7644034564506796</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7367177618456608</v>
+        <v>0.7372283342232606</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.240884770651377</v>
+        <v>1.173907946596373</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.022837827327109</v>
+        <v>1.027790994383551</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.586827977109877</v>
+        <v>1.543813369725527</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.077527604783199</v>
+        <v>1.024528294530079</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.9796260193247193</v>
+        <v>0.9473385670556382</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9784043140794623</v>
+        <v>0.9546737055352352</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.326490273858695</v>
+        <v>1.291566150478367</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.359129097571937</v>
+        <v>1.347586304165517</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002141</t>
+          <t>X &gt; 0.0002266</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2547</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9646595372025288</v>
+        <v>0.9118670566147813</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4711567874868194</v>
+        <v>0.5232995093624808</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.4300543913333</v>
+        <v>1.364245117298033</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.521094581943608</v>
+        <v>1.454990215264182</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.396712415342115</v>
+        <v>1.300828048890345</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.010279249029431</v>
+        <v>0.8905533327100486</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.692774791347134</v>
+        <v>1.574119726837509</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.500323644618057</v>
+        <v>1.421643801550125</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.324996773234965</v>
+        <v>2.268888174831211</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.553570912540891</v>
+        <v>1.506763222441499</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.662841496823873</v>
+        <v>1.678100288529443</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.500987310089705</v>
+        <v>1.523573082094764</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.731692975881181</v>
+        <v>1.739730086186789</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.525547982212935</v>
+        <v>1.579761111626475</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.001045</t>
+          <t>X &gt; 0.001056</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.116359405821541</v>
+        <v>1.188867766949755</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3797888474409987</v>
+        <v>0.5217685123306239</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.329061728118873</v>
+        <v>1.257653952706292</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.416679287557258</v>
+        <v>1.430091185410333</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.9447892773653663</v>
+        <v>0.9220200921563944</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4322741339399272</v>
+        <v>0.3667683077769652</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.394484814342057</v>
+        <v>1.370848164037021</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.055347940278132</v>
+        <v>1.03278371711194</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.12755891124322</v>
+        <v>2.127525159549918</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.27764011491336</v>
+        <v>1.285480292757768</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.414235884980819</v>
+        <v>1.404259408893992</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.277965573172317</v>
+        <v>1.273675846077694</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.607925062335731</v>
+        <v>1.628573637002162</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.364177144487151</v>
+        <v>1.43275539132862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001875</t>
+          <t>X &gt; 0.001885</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2105</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.594913353351899</v>
+        <v>1.55800548826344</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.9576845051358163</v>
+        <v>0.9469382551251755</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.012177725043358</v>
+        <v>1.905018556187919</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.952649547948617</v>
+        <v>1.987554112554108</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.366921664682145</v>
+        <v>1.403608001905219</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.047597402097111</v>
+        <v>1.134588688890886</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.416444309698683</v>
+        <v>1.452899913734598</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.186679889927134</v>
+        <v>1.31866355316177</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.149598978789541</v>
+        <v>2.256296990888501</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.442130324909826</v>
+        <v>1.554513628152662</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.56981283236663</v>
+        <v>1.709725841976621</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.604190984721953</v>
+        <v>1.747899585895077</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.924104149382309</v>
+        <v>2.044980391437093</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.674780417186035</v>
+        <v>1.846779176752698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002706</t>
+          <t>X &gt; 0.002715</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.248444275643891</v>
+        <v>2.347966777733099</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.542471180559374</v>
+        <v>1.613974880235702</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.952951436942186</v>
+        <v>2.890022281970325</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.481426033484588</v>
+        <v>2.52810304449649</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.99784107557489</v>
+        <v>2.03885390354457</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.419941582234053</v>
+        <v>1.52262096741633</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.913237520433931</v>
+        <v>1.954037048775888</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.33669980166087</v>
+        <v>1.378854917151429</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.401942203020319</v>
+        <v>2.412166197645938</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.442494381498783</v>
+        <v>1.478928426458971</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.785438349196973</v>
+        <v>1.853572776375145</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.600758451168936</v>
+        <v>1.692801363767401</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.03421380350003</v>
+        <v>2.09600032197509</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.712004248247112</v>
+        <v>1.797400058032082</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.003536</t>
+          <t>X &gt; 0.003544</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.081784934095879</v>
+        <v>3.166604018602435</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.278554247058189</v>
+        <v>2.325196327441112</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.749934728455017</v>
+        <v>3.701797764455556</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.979258971142471</v>
+        <v>3.060968896229006</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.312269289346659</v>
+        <v>2.379041527916776</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.708742418080845</v>
+        <v>1.788861387048051</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.304203537440756</v>
+        <v>2.370878819673493</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.193219890434442</v>
+        <v>1.198105185254164</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.135035776941116</v>
+        <v>2.097658750081443</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.478415949683423</v>
+        <v>1.46675621428254</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.595879739876843</v>
+        <v>1.621320819985264</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.436958923159992</v>
+        <v>1.486437364299967</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.085581458481784</v>
+        <v>2.09423713740987</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.859995380790856</v>
+        <v>1.892541497171528</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.004367</t>
+          <t>X &gt; 0.004374</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.031805634847295</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.620860839364781</v>
+        <v>2.663467846713921</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.463743775597393</v>
+        <v>4.277451866121226</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.819277561161073</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.972346032756732</v>
+        <v>1.910364758661977</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.115399074737496</v>
+        <v>2.183150277480905</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.383362818145429</v>
+        <v>2.431374497135749</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.298533556598073</v>
+        <v>1.34778111899179</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.550292712816614</v>
+        <v>2.590907332457682</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.854814070926899</v>
+        <v>1.92163825705228</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.881773144326942</v>
+        <v>1.994282445847119</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.993371373902342</v>
+        <v>2.129788703706978</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.577081524449937</v>
+        <v>2.708498160218006</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.185056556915853</v>
+        <v>2.338347975793752</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.005197</t>
+          <t>X &gt; 0.005203</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.971774136441532</v>
+        <v>1.9425783420889</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.26815785783171</v>
+        <v>2.307453204984988</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.544695665277239</v>
+        <v>3.397945272328911</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.910761105987234</v>
+        <v>2.043599257884964</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.558172574247152</v>
+        <v>1.647114495411714</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.391294050493194</v>
+        <v>1.548842500315978</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.585135223260458</v>
+        <v>1.766479546526512</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2824119833734358</v>
+        <v>0.4657673798351922</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.89273901905122</v>
+        <v>2.058846639508722</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.321371754754786</v>
+        <v>1.513569590727172</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.395222128528012</v>
+        <v>1.641654483441606</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9653477274942972</v>
+        <v>1.23513720593661</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.216506066381449</v>
+        <v>2.474716030475058</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.235185077796459</v>
+        <v>1.421435311095074</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.006028</t>
+          <t>X &gt; 0.006033</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.604239320443781</v>
+        <v>1.57504352609115</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.589925526171406</v>
+        <v>2.638586809174662</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.499301606854154</v>
+        <v>4.431269994622895</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.901416151364181</v>
+        <v>3.065181653789246</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.363126598268487</v>
+        <v>2.345782915599123</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.890915374447346</v>
+        <v>2.963792830275352</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.036619761724957</v>
+        <v>3.133286338288102</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.647892131763101</v>
+        <v>1.746855188951933</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.084605827774887</v>
+        <v>3.157862937554583</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.465101777988806</v>
+        <v>2.679656476555266</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.3756079930005</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.064364025540158</v>
+        <v>2.255298167762845</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.833153264392649</v>
+        <v>4.006054985306143</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.906815181900292</v>
+        <v>3.100365436236054</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.006858</t>
+          <t>X &gt; 0.006862</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>696</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.751508646653598</v>
+        <v>1.644615968809298</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.091805922378839</v>
+        <v>3.070034872192117</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.139563273255973</v>
+        <v>4.968560494192602</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3.833006807648935</v>
+        <v>3.809046254604986</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.294717254553241</v>
+        <v>3.319797113653067</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.161056801429709</v>
+        <v>3.162783205537899</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.220024603083075</v>
+        <v>3.245393591957132</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.747208832859563</v>
+        <v>1.776695502060903</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.548295641854025</v>
+        <v>2.538685290099068</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>2.288744801106176</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.637353848183508</v>
+        <v>1.797660307659037</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.671732000538832</v>
+        <v>1.855827045023929</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.69410988285761</v>
+        <v>3.842799430635438</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.339385762969201</v>
+        <v>2.511384522535863</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.007689</t>
+          <t>X &gt; 0.007692</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>565</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.094305208403703</v>
+        <v>2.966919977233154</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.607012920649602</v>
+        <v>3.680562680063169</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.044099942974206</v>
+        <v>5.937001370193691</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.873440130810359</v>
+        <v>3.946744068652194</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.866124029042105</v>
+        <v>3.987530263389317</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.809515757792234</v>
+        <v>3.906958891748886</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.724805398526065</v>
+        <v>3.846302802523425</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.195789852084467</v>
+        <v>2.320399370761983</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.957816545119201</v>
+        <v>2.031073654898897</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.992853501001733</v>
+        <v>2.092200826296306</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.434170041856582</v>
+        <v>1.534078077875257</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.999521645539339</v>
+        <v>2.123218266567584</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.703264597535671</v>
+        <v>3.851954145313499</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.39802679643477</v>
+        <v>3.570025556001433</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.008519</t>
+          <t>X &gt; 0.008521</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>451</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.503562905164095</v>
+        <v>4.348295254759037</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.553130692366338</v>
+        <v>5.64122436429345</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.262572167921718</v>
+        <v>8.123592570669011</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.175502411288356</v>
+        <v>6.262326169405817</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.30240132825918</v>
+        <v>6.436793842613184</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.156316377849926</v>
+        <v>6.267101485325917</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.184688058495055</v>
+        <v>5.321489643888064</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.495889924686146</v>
+        <v>4.634417945451631</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.326260318052505</v>
+        <v>3.399517427832201</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.806718461855681</v>
+        <v>3.906065787150254</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.158558323551148</v>
+        <v>3.258466359569823</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.971206985884301</v>
+        <v>3.094903606912546</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.9900805228148</v>
+        <v>5.138770070592628</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.772357192996978</v>
+        <v>4.94435595256364</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>345</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.171257882509124</v>
+        <v>3.142062088156493</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.719492079300373</v>
+        <v>2.718305292855717</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.67254678150185</v>
+        <v>6.672393391497529</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.512916852626454</v>
+        <v>6.512422360248451</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.13404758938583</v>
+        <v>7.182593509151602</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.982146256702066</v>
+        <v>6.006103665651679</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.158305462653288</v>
+        <v>4.206317141643609</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.560802036257861</v>
+        <v>4.610049598651578</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.920109734807546</v>
+        <v>3.993366844587243</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.968741663115374</v>
+        <v>6.068088988409947</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.638998367355434</v>
+        <v>4.762694988383679</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.378267803897096</v>
+        <v>5.526957351674923</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.314148381659855</v>
+        <v>5.486147141226517</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>251</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.295976399744525</v>
+        <v>3.266780605391894</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.473634928194649</v>
+        <v>4.472448141749993</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.461333662961522</v>
+        <v>8.461180272957201</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.7947460575459</v>
+        <v>7.794251565167897</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.451675627956178</v>
+        <v>8.500221547721949</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.14745603209326</v>
+        <v>9.171413441042873</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.469120174819125</v>
+        <v>7.517131853809445</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.400457905534374</v>
+        <v>7.449705467928091</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.949037501999648</v>
+        <v>5.022294611779344</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.286369701685722</v>
+        <v>7.385717026980295</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.488043045417562</v>
+        <v>5.587951081436238</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.725608448768902</v>
+        <v>4.849305069797147</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.297489467965455</v>
+        <v>6.446179015743283</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.328005994686009</v>
+        <v>5.500004754252672</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.834873443149853</v>
+        <v>3.805677648797221</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.328950507980771</v>
+        <v>4.327763721536115</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.61838964954152</v>
+        <v>7.618236259537198</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.748614793129882</v>
+        <v>7.748120300751879</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.789272608455235</v>
+        <v>8.837818528221007</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.507699269669274</v>
+        <v>7.531656678618887</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.844041541982051</v>
+        <v>5.892053220972372</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.903288687668997</v>
+        <v>5.952536250062714</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.737043373251474</v>
+        <v>3.81030048303117</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.045019313763731</v>
+        <v>6.144366639058305</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.787686576556169</v>
+        <v>4.887594612574844</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.295748939437807</v>
+        <v>4.419445560466052</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.401913875598083</v>
+        <v>4.550603423375911</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.153965315298301</v>
+        <v>5.325964074864963</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>157</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.570039383478388</v>
+        <v>3.540843589125757</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.869681315892265</v>
+        <v>3.868494529447609</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.93350865725187</v>
+        <v>7.933355267247549</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.61150450147718</v>
+        <v>10.61101000909918</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.98404297385918</v>
+        <v>12.03258889362495</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.0075316531758</v>
+        <v>11.03148906212542</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.648935943591169</v>
+        <v>9.69694762258149</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.907981949485958</v>
+        <v>7.957229511879675</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.299229092326236</v>
+        <v>5.372486202105932</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.270966346951795</v>
+        <v>8.370313672246368</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.066265188691602</v>
+        <v>8.166173224710278</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.463700665887686</v>
+        <v>7.58739728691593</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.680492487733517</v>
+        <v>7.829182035511344</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.543170813119282</v>
+        <v>8.715169572685944</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>116</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1052908660173699</v>
+        <v>0.07609507166473861</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.390656497091477</v>
+        <v>5.389469710646821</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.720023043370915</v>
+        <v>6.719869653366594</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>9.436455083511007</v>
+        <v>9.435960591133004</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.34644139248427</v>
+        <v>12.39498731225004</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>12.64381542211936</v>
+        <v>12.66777283106897</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.69703609733595</v>
+        <v>11.74504777632627</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.643760556997492</v>
+        <v>8.693008119391209</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.134502538405748</v>
+        <v>5.207759648185444</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.594928569662102</v>
+        <v>8.694275894956675</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.390227411401909</v>
+        <v>8.490135447420585</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>9.286674529274471</v>
+        <v>9.410371150302716</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.59066160699554</v>
+        <v>10.73935115477337</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.67846622273931</v>
+        <v>11.85046498230597</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>10.19361216211611</v>
+        <v>10.19242537567145</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.98931696783726</v>
+        <v>10.98916357783294</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.500494492378</v>
+        <v>13.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>14.1526811297585</v>
+        <v>14.20122704952427</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>14.45005515939359</v>
+        <v>14.4740125683432</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.36534480012742</v>
+        <v>14.41335647911774</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.755419013483532</v>
+        <v>6.804666575877249</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>9.415946632059473</v>
+        <v>9.515293957354046</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.020769283323091</v>
+        <v>8.120677319341766</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>11.43216080402011</v>
+        <v>11.60415956358677</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1249 +3904,1249 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01058</t>
+          <t>X &lt; -0.01056</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.1291594439345971</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-14.01068303216275</v>
+        <v>-14.01083642216707</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.216611507273079</v>
+        <v>-2.192654098323466</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.720771462706942</v>
+        <v>-8.671523900313225</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.400801238277339</v>
+        <v>-6.327544128497642</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.389467947407866</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.009752</t>
+          <t>X &lt; -0.009727</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.858889794708361</v>
+        <v>2.82969400035573</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2768299152367675</v>
+        <v>0.2756431287921117</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.826679333595933</v>
+        <v>-9.826832723600255</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.900337685153211</v>
+        <v>-2.900832177531214</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.467753451841133</v>
+        <v>-2.419207532075362</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.141253208613819</v>
+        <v>-3.117295799664205</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.167711140695516</v>
+        <v>-5.119699461705196</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.518274930113321</v>
+        <v>-9.469027367719605</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.637509513820568</v>
+        <v>-7.564252404040872</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.633059378111589</v>
+        <v>-3.533712052817016</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-5.779508109187319</v>
+        <v>-5.679600073168643</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.745129956831995</v>
+        <v>-5.621433335803751</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.310911878106573</v>
+        <v>-1.162222330328746</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.085176227880041</v>
+        <v>-0.9131774683133784</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.008922</t>
+          <t>X &lt; -0.008897</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.316185418741014</v>
+        <v>3.286989624388383</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9803616445177639</v>
+        <v>0.9791748580731081</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.211511189512635</v>
+        <v>-5.211664579516956</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.458097640127178</v>
+        <v>-1.458592132505181</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1775258502553925</v>
+        <v>0.2260717700211643</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4748998798904793</v>
+        <v>0.4988572888400924</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.783723522853954</v>
+        <v>-1.735711843863633</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.424705210118951</v>
+        <v>-4.375457647725234</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.761049685482313</v>
+        <v>-3.687792575702616</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.192481234275256</v>
+        <v>-1.092573198256581</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.781291487717041</v>
+        <v>-4.657594866688797</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8536162540739198</v>
+        <v>-0.7049267062960922</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.352518285006809</v>
+        <v>-1.180519525440147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.008091</t>
+          <t>X &lt; -0.008068</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.005271814769514549</v>
+        <v>0.2072794794608441</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5009419026037065</v>
+        <v>-0.2889410839558835</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.420575165811783</v>
+        <v>-6.117461680966237</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.317974331615687</v>
+        <v>-1.639751552795033</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3536808666698406</v>
+        <v>0.04491234973130531</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6510548963049274</v>
+        <v>0.3176978685502334</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.196086402187767</v>
+        <v>-2.460349525023055</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.768127421665113</v>
+        <v>-4.013138807145523</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.93408195387849</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.364111247445919</v>
+        <v>-1.613070431879919</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.778757157087334</v>
+        <v>-3.991123922894268</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.401837568267915</v>
+        <v>-5.563391968138063</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.402098918818893</v>
+        <v>-1.610723807745373</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.281335644282983</v>
+        <v>-2.448635467469138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007261</t>
+          <t>X &lt; -0.007238</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.187812582258488</v>
+        <v>-0.8007101154852663</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2127917787705869</v>
+        <v>0.1802153634614356</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.073080404904942</v>
+        <v>-6.623779035109678</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.339406985454517</v>
+        <v>-0.9383394383394403</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2774758752428923</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.873425957190982</v>
+        <v>-2.436854342523709</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.544343213008879</v>
+        <v>-5.488963423202172</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.011411856795618</v>
+        <v>-5.954796183585515</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6.934462978835633</v>
+        <v>-6.846469647423163</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.767140395855144</v>
+        <v>-4.678845236785158</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.971841554115336</v>
+        <v>-4.882985684321248</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.633476324038945</v>
+        <v>-3.510575164118464</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.838775156571032</v>
+        <v>-3.688880729453523</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.00643</t>
+          <t>X &lt; -0.006409</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3497684895507476</v>
+        <v>-0.5620598768350433</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6494791727785056</v>
+        <v>-0.1971850139389417</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.634414491959781</v>
+        <v>-5.136377547708193</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5861565614861703</v>
+        <v>-0.1363636363636331</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5148981477132182</v>
+        <v>0.6730885213857434</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.482809789864817</v>
+        <v>-1.326853232522609</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.190470968803105</v>
+        <v>-3.984911919150669</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.001801907671819</v>
+        <v>-4.126069354858686</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.062784064194595</v>
+        <v>-4.163041963995482</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.961883188393301</v>
+        <v>-2.06479262273254</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.838715494194481</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.755157013970297</v>
+        <v>-4.483493605631004</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.224488195152567</v>
+        <v>-2.281248934792231</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.310227954762105</v>
+        <v>-3.330905371478167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.0056</t>
+          <t>X &lt; -0.005579</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.043888147011337</v>
+        <v>0.8404036390305407</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.30476471713289</v>
+        <v>2.092278100266441</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.095228599737034</v>
+        <v>-4.229294939594652</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.87623061019567</v>
+        <v>-1.77982326951399</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.109037134570734</v>
+        <v>-0.9804126166514848</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.378242739400392</v>
+        <v>-2.511750809172753</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.551725944619577</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.102222472430206</v>
+        <v>-3.811435535070224</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.163204628952982</v>
+        <v>-4.10614010296991</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.180662692298554</v>
+        <v>-3.125844972444682</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.076463326998528</v>
+        <v>-2.041325626166341</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.612765802915462</v>
+        <v>-3.27181868261588</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.200455923244576</v>
+        <v>-1.862852897839502</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.498280482442134</v>
+        <v>-2.129271953349907</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.004769</t>
+          <t>X &lt; -0.00475</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3248585356678291</v>
+        <v>-0.4609314970181373</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1173434616174305</v>
+        <v>0.2099897784817557</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.178865294800865</v>
+        <v>-4.282108865570656</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.299035196040577</v>
+        <v>-2.512880562060893</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.808518164774128</v>
+        <v>-1.977539539078393</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.9226667688839</v>
+        <v>-1.909672053046343</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.447706346257064</v>
+        <v>-3.404754371780008</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.159652169628885</v>
+        <v>-2.231242869868268</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.839191027182586</v>
+        <v>-2.882969577365706</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.833439720419669</v>
+        <v>-1.862535863098728</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.1824707755870776</v>
+        <v>-0.2224140155528502</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9728348912729885</v>
+        <v>-0.983919409335499</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.9806146105657803</v>
+        <v>-0.9692412703255613</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.579621228380482</v>
+        <v>-1.539868539457736</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.003939</t>
+          <t>X &lt; -0.003921</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.9254354569315169</v>
+        <v>-1.113156459711711</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.320206841686549</v>
+        <v>-4.321463984450261</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.104561553412609</v>
+        <v>-3.198202459791865</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.475906198327991</v>
+        <v>-3.521888686836505</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.676027995070207</v>
+        <v>-1.759036942852013</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.764077252499987</v>
+        <v>-3.887993911784896</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.306533526729879</v>
+        <v>-2.529614400194767</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-3.370860164858009</v>
+        <v>-3.561611884953457</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.712417757174492</v>
+        <v>-1.897878276713719</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4121021930266551</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.9541849404881404</v>
+        <v>-1.214664590533332</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.709344169010933</v>
+        <v>-1.941497475637796</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.488633644412531</v>
+        <v>-2.687477489244316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003108</t>
+          <t>X &lt; -0.003091</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.879852200747116</v>
+        <v>-2.970032981260175</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.831463825725841</v>
+        <v>-2.056495217532984</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.220916061544713</v>
+        <v>-4.158511786662402</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.02375888407245</v>
+        <v>-4.028627745447722</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-3.896269475783321</v>
+        <v>-4.123658752365479</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.666804900209485</v>
+        <v>-2.931030920800161</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.949917389968334</v>
+        <v>-3.976367831659211</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.01600955794504</v>
+        <v>-3.189686896737093</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.610325047801147</v>
+        <v>-3.88542103420064</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.326910510797674</v>
+        <v>-2.601212724370029</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.73161166905787</v>
+        <v>-2.014839337914026</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.624425328006502</v>
+        <v>-1.956672600549133</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.044576181319911</v>
+        <v>-2.351830527112959</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.88693131881034</v>
+        <v>-3.288556416085733</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.002277</t>
+          <t>X &lt; -0.002262</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.534391966363231</v>
+        <v>-2.563021877797041</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.471781267983204</v>
+        <v>-1.500696317450249</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.898638214235575</v>
+        <v>-3.799196210526851</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.860676675890524</v>
+        <v>-2.93961233707784</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.920904359317547</v>
+        <v>-2.031233597919915</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.862145767834242</v>
+        <v>-2.990572218554334</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.987499375737109</v>
+        <v>-2.127696178141555</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.227474029580364</v>
+        <v>-3.332397025070286</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.148132375749448</v>
+        <v>-2.139240467881024</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.709746717289377</v>
+        <v>-1.706438240257874</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.509536807117428</v>
+        <v>-1.542114390366443</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.144279935108941</v>
+        <v>-2.043429429456808</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.776913383594859</v>
+        <v>-2.749798580180297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.001447</t>
+          <t>X &lt; -0.001432</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.169250847987605</v>
+        <v>-2.067633948780788</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7528323105972916</v>
+        <v>-0.73045705163576</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.284736375672892</v>
+        <v>-3.071097694817716</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.465382767616909</v>
+        <v>-3.249968366443127</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.57764736527588</v>
+        <v>-2.322034159299385</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.191146775926001</v>
+        <v>-1.960674681224475</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.988869612910527</v>
+        <v>-2.772560440841744</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.893321481822525</v>
+        <v>-1.772677405193441</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.024776430495173</v>
+        <v>-2.963154894543194</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.268986038600232</v>
+        <v>-2.189822871986394</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.800659288105493</v>
+        <v>-1.684114162468347</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.538877841992978</v>
+        <v>-1.448485135839931</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.137759705136602</v>
+        <v>-2.021105351667281</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.269486074570473</v>
+        <v>-2.215716212810747</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0006164</t>
+          <t>X &lt; -0.0006029</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1343</v>
+        <v>1352</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.478688859042144</v>
+        <v>-1.366200385772594</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.04607391275927597</v>
+        <v>0.002652049366759002</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.777148192837252</v>
+        <v>-1.64569848507341</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.979233803100662</v>
+        <v>-1.919919814306816</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.477404485468277</v>
+        <v>-1.449050786868781</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.254324660885196</v>
+        <v>-1.25012051177216</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.156271275723427</v>
+        <v>-2.010463603238932</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.692093820646399</v>
+        <v>-1.697728464979328</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.719618728098538</v>
+        <v>-2.622275038613175</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.710801464948851</v>
+        <v>-1.596991193392654</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.577445002391201</v>
+        <v>-1.505273652763059</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.502346447950998</v>
+        <v>-1.447106915398166</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.220337956513845</v>
+        <v>-2.138122830127678</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.292442961536757</v>
+        <v>-2.258900453319399</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002141</t>
+          <t>X &lt; 0.0002266</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1603</v>
+        <v>1614</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.455434364903532</v>
+        <v>-1.366017823650125</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.580604298862319</v>
+        <v>-0.6610069063322612</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.218383763169875</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.304409558794703</v>
+        <v>-2.191301272984447</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.09643045517398</v>
+        <v>-1.937976156510622</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.363733042454321</v>
+        <v>-1.1701411327412</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.319090167889648</v>
+        <v>-2.126522630420816</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.006841335584532</v>
+        <v>-1.878286159120101</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.187923056513036</v>
+        <v>-3.092458272593944</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.012921303657777</v>
+        <v>-1.933635056630735</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.246253413606148</v>
+        <v>-2.261691241465464</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.928821214125655</v>
+        <v>-1.955693029503294</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.286627927788189</v>
+        <v>-2.288893087417812</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.964595278325497</v>
+        <v>-2.039848225402444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.001045</t>
+          <t>X &lt; 0.001056</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1807</v>
+        <v>1819</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.3783801981198</v>
+        <v>-1.467301726094448</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3434802933886942</v>
+        <v>-0.5257806773315323</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.675407135696105</v>
+        <v>-1.578135570146777</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.736681459083663</v>
+        <v>-1.74868596532518</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.116669853878207</v>
+        <v>-1.08472258568402</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3481157646051543</v>
+        <v>-0.262788247535056</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.481391245284122</v>
+        <v>-1.447449381688124</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.035593581504763</v>
+        <v>-1.004438374514123</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.311374191920414</v>
+        <v>-2.305841989698195</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.25361400987687</v>
+        <v>-1.260511692008507</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.483297683430457</v>
+        <v>-1.464652139544597</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.252690743841185</v>
+        <v>-1.241559618782226</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.672841597154594</v>
+        <v>-1.691692806478549</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.361340658546105</v>
+        <v>-1.442647944463182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001875</t>
+          <t>X &lt; 0.001885</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2045</v>
+        <v>2056</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.579795718795431</v>
+        <v>-1.539238038479219</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.8529399219420739</v>
+        <v>-0.8408617255768149</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.027058603336179</v>
+        <v>-1.914211364376953</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.920001191275574</v>
+        <v>-1.953063206827181</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.311320170420281</v>
+        <v>-1.347849724042305</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8902468150547307</v>
+        <v>-0.9778824753885829</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.170079125540411</v>
+        <v>-1.206941226741463</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9277713929865214</v>
+        <v>-1.063130348339911</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.818426560734288</v>
+        <v>-1.926951206503944</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.128603219131008</v>
+        <v>-1.242997686151604</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.306469184120566</v>
+        <v>-1.447138133687695</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.294105461961593</v>
+        <v>-1.43760952861853</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.616504604620062</v>
+        <v>-1.735491190590906</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.363857358746223</v>
+        <v>-1.535084460871261</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002706</t>
+          <t>X &lt; 0.002715</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.709707804313275</v>
+        <v>-1.784236504647872</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.092959021627308</v>
+        <v>-1.147089080837027</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.279415300037748</v>
+        <v>-2.224003841141489</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.869512858761425</v>
+        <v>-1.900927564532864</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.484384507307148</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9494952186975709</v>
+        <v>-1.026597932267308</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.248797852641843</v>
+        <v>-1.27812746803103</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.7912492888739067</v>
+        <v>-0.8229353631019407</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.539221569913643</v>
+        <v>-1.54425356676397</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8196940159523081</v>
+        <v>-0.8475032796408826</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.12957757652098</v>
+        <v>-1.180013431926653</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9425186987031182</v>
+        <v>-1.012692146815851</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.276685029230627</v>
+        <v>-1.322233635023515</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.027132590757162</v>
+        <v>-1.092383721821619</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.003536</t>
+          <t>X &lt; 0.003544</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2599</v>
+        <v>2608</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.790731981454599</v>
+        <v>-1.840895763701511</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.254678810714744</v>
+        <v>-1.28258145306387</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.204556669074357</v>
+        <v>-2.173451372544925</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.708912370904535</v>
+        <v>-1.755765657448904</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.305686478321213</v>
+        <v>-1.344669839656198</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.8725254857677101</v>
+        <v>-0.918803570741602</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.149248133820358</v>
+        <v>-1.18862704017053</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4816517656540853</v>
+        <v>-0.4850053250547077</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.9652232421922378</v>
+        <v>-0.9432724573627027</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6029033368289305</v>
+        <v>-0.5969118445069341</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.724423939552608</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.5767206961897244</v>
+        <v>-0.6066785846994733</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.9584100110415932</v>
+        <v>-0.9635076496304933</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8266750119530712</v>
+        <v>-0.8465415757646824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.004367</t>
+          <t>X &lt; 0.004374</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2855</v>
+        <v>2869</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.329485465286616</v>
+        <v>-1.328735869362319</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.091404286891972</v>
+        <v>-1.105102669598082</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.991236510098418</v>
+        <v>-1.89752394389108</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.214190264206202</v>
+        <v>-1.193026028213794</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8257796922231009</v>
+        <v>-0.7942180850513054</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8239789825650874</v>
+        <v>-0.8505723804588712</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8737487408529176</v>
+        <v>-0.8925291887588855</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3782838210232171</v>
+        <v>-0.3995382258205922</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.8746607121368157</v>
+        <v>-0.8891570745117008</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5863019063905384</v>
+        <v>-0.6143273791638464</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6316349953932985</v>
+        <v>-0.6791435494446247</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6477877110789265</v>
+        <v>-0.7061733648961379</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9084207845817787</v>
+        <v>-0.961958469160308</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.7332132265027838</v>
+        <v>-0.7981209721897642</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.005197</t>
+          <t>X &lt; 0.005203</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3073</v>
+        <v>3086</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6494735670011238</v>
+        <v>-0.6367268119670939</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7047439388331895</v>
+        <v>-0.7168753397682011</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.211905933774752</v>
+        <v>-1.158002981098328</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.6102974079046604</v>
+        <v>-0.6552353240035131</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4822189042330294</v>
+        <v>-0.5126274444078476</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3619261082838818</v>
+        <v>-0.4163758095896668</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3640924293098138</v>
+        <v>-0.427142827400985</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.09586659232019201</v>
+        <v>0.03101506282786914</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4020079587823062</v>
+        <v>-0.45917865346334</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2266396842350105</v>
+        <v>-0.2937980732405805</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.2831504640296956</v>
+        <v>-0.3684048420201975</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1004855492228742</v>
+        <v>-0.194981664057849</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5349076838307454</v>
+        <v>-0.6225335005666039</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.193286641472902</v>
+        <v>-0.2581679986759866</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.006028</t>
+          <t>X &lt; 0.006033</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3282</v>
+        <v>3295</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3861983620461942</v>
+        <v>-0.3769802061275271</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6009060094512506</v>
+        <v>-0.612659370091265</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.161638160645964</v>
+        <v>-1.141583362178316</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7114478787381273</v>
+        <v>-0.7532664186207612</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5649470336308369</v>
+        <v>-0.5598121737991164</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6461961070704518</v>
+        <v>-0.6645155701849461</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6232897537245279</v>
+        <v>-0.6482061877798913</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.2527492173124415</v>
+        <v>-0.2789916296730084</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5708361521516281</v>
+        <v>-0.5888569010293381</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4302986219764122</v>
+        <v>-0.4862225728249143</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4354168440959185</v>
+        <v>-0.5083793988869374</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3231368865766768</v>
+        <v>-0.3726469280367581</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7871782577202922</v>
+        <v>-0.8284844662510693</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.5444214193628554</v>
+        <v>-0.5928922465151203</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.006858</t>
+          <t>X &lt; 0.006862</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3454</v>
+        <v>3465</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3170383617518979</v>
+        <v>-0.2949219514692629</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5433427467949485</v>
+        <v>-0.5393320755104583</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.009240030719738</v>
+        <v>-0.975224940959734</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7192349698456937</v>
+        <v>-0.7147587511826003</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6067484867314761</v>
+        <v>-0.6125210303528448</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5247735935980842</v>
+        <v>-0.5257816449341703</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4782869605803413</v>
+        <v>-0.4844066607203388</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.178244625382419</v>
+        <v>-0.1851342449988067</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2811547673732733</v>
+        <v>-0.2797603565858751</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2476353999436114</v>
+        <v>-0.2515539582828055</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1469235965479783</v>
+        <v>-0.1800355242035039</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1252427759618087</v>
+        <v>-0.1634195654184794</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5291547511061552</v>
+        <v>-0.5585774919823052</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2582188799901601</v>
+        <v>-0.2933873339601263</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.007689</t>
+          <t>X &lt; 0.007692</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3585</v>
+        <v>3596</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4520110833414606</v>
+        <v>-0.4313978559291129</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4918797160363226</v>
+        <v>-0.5030477123716395</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9273629410562236</v>
+        <v>-0.9096558501046346</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.55970817004998</v>
+        <v>-0.5707350901525672</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.554370305172732</v>
+        <v>-0.5733620313911132</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4923593237946235</v>
+        <v>-0.5075504148850669</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4228087686497588</v>
+        <v>-0.4421470771076486</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1785826573602449</v>
+        <v>-0.198679055627224</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.08497685838609925</v>
+        <v>-0.09680134540828789</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1115116067389792</v>
+        <v>-0.1275631855030994</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.04978335244694421</v>
+        <v>-0.06612060071540071</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1112470842148596</v>
+        <v>-0.1313282612477664</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3763172571697027</v>
+        <v>-0.3997206771171875</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3301424436387919</v>
+        <v>-0.3575439164704406</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.008519</t>
+          <t>X &lt; 0.008521</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3699</v>
+        <v>3710</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5143212029481461</v>
+        <v>-0.4950661505183618</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6024766857108119</v>
+        <v>-0.6130416646786827</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.9828303816685917</v>
+        <v>-0.9655215220134608</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7033725491811467</v>
+        <v>-0.7136903161372175</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.714786893049336</v>
+        <v>-0.7312763445175889</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6455811528599469</v>
+        <v>-0.659159344489737</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.472884069402042</v>
+        <v>-0.4900214490179948</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3855102327088744</v>
+        <v>-0.4029217084270513</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1887267756629214</v>
+        <v>-0.197633213929933</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2676432500181249</v>
+        <v>-0.2796902722020818</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2141616420454469</v>
+        <v>-0.226442837635652</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1646387225027723</v>
+        <v>-0.180146091076594</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4074744601060374</v>
+        <v>-0.42549891816914</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3828084927010167</v>
+        <v>-0.4039266897825087</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3805</v>
+        <v>3816</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2546195402252849</v>
+        <v>-0.2510363482612377</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1754136247771143</v>
+        <v>-0.1747936122371883</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5822613490240869</v>
+        <v>-0.5805727567322521</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5427558352759974</v>
+        <v>-0.5411470390560922</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5949903562454466</v>
+        <v>-0.5980259850228862</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.440731997325905</v>
+        <v>-0.4418073160959324</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2226729883101015</v>
+        <v>-0.2267292177296696</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.2556142111419248</v>
+        <v>-0.2596976313441033</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1447082499008872</v>
+        <v>-0.1514620756817493</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3500836971107901</v>
+        <v>-0.3588022779987412</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1725080276012818</v>
+        <v>-0.181795280067206</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.228465457863571</v>
+        <v>-0.239924183957875</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2923362004591112</v>
+        <v>-0.3060627377040248</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2883197666575796</v>
+        <v>-0.3043459769942487</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3899</v>
+        <v>3910</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1803025336018393</v>
+        <v>-0.1777131504031715</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2184125301438229</v>
+        <v>-0.2177152231483959</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5226791349516873</v>
+        <v>-0.5212018537260619</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4553948472411946</v>
+        <v>-0.4540816326530575</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4937096681164377</v>
+        <v>-0.4957923553287742</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4895526263877343</v>
+        <v>-0.4898902975504811</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3299957016646999</v>
+        <v>-0.3325010162929871</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3221982049787613</v>
+        <v>-0.3248144300082529</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1129889822273853</v>
+        <v>-0.1179108498988484</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2826368751328019</v>
+        <v>-0.2889496614015812</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1911366989570666</v>
+        <v>-0.1977484409444656</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1167498800281876</v>
+        <v>-0.1252751369830918</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2148202674518558</v>
+        <v>-0.2248611906008691</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1541433765390181</v>
+        <v>-0.1660267718169663</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3960</v>
+        <v>3971</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1527005762177112</v>
+        <v>-0.1506740738829748</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.139433442832825</v>
+        <v>-0.138983110394328</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3443401414431264</v>
+        <v>-0.3433804895177701</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3264216645129636</v>
+        <v>-0.3254925180320782</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3723881572155534</v>
+        <v>-0.3740301890495559</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2628864688706258</v>
+        <v>-0.2634783063680857</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1322364355430636</v>
+        <v>-0.1345139511056388</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.13169286606405</v>
+        <v>-0.1340405136973288</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.02296625106392014</v>
+        <v>0.01886767566064407</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1066616039695631</v>
+        <v>-0.111839915062852</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.07014308465210917</v>
+        <v>-0.07545468152098778</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.02158148910705648</v>
+        <v>-0.02834015098095222</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.0236033382899592</v>
+        <v>-0.03173611126129572</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.06134568948639441</v>
+        <v>-0.07066146026473064</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3993</v>
+        <v>4004</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1094731947879666</v>
+        <v>-0.1078215585190492</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.08461148689405462</v>
+        <v>-0.08432476661653965</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2910693125490198</v>
+        <v>-0.2902647563899166</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3721367484770681</v>
+        <v>-0.371094028044709</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4221742996696491</v>
+        <v>-0.4232671538386157</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3361292468857968</v>
+        <v>-0.3363183436826347</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2322742474916382</v>
+        <v>-0.2338636654846127</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.160595704481679</v>
+        <v>-0.1624394685355242</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.00772374715082691</v>
+        <v>-0.01110136281566554</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1433061408535536</v>
+        <v>-0.1475232653434233</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1588388962850971</v>
+        <v>-0.1630404602582232</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1104166623012119</v>
+        <v>-0.115856749227305</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1159155000443306</v>
+        <v>-0.1225025625627225</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1515034655945868</v>
+        <v>-0.1590771996499925</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4034</v>
+        <v>4045</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.02711460944587429</v>
+        <v>0.02808433085476025</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.08814760061251548</v>
+        <v>-0.0878661838905046</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1729056467957406</v>
+        <v>-0.1724312376080306</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2270736862287492</v>
+        <v>-0.2264400211379325</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3067608216448647</v>
+        <v>-0.3076648150656709</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2680240564590193</v>
+        <v>-0.2681537282272402</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1908117382117496</v>
+        <v>-0.1920118281261907</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.09983794078331698</v>
+        <v>-0.1013295920295647</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.05087822033452483</v>
+        <v>0.04811724716373078</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.06717796993586234</v>
+        <v>-0.07055322419578403</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.08461307274047414</v>
+        <v>-0.08796186755829183</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.08586912952051762</v>
+        <v>-0.09006765920284465</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1203583477111181</v>
+        <v>-0.1253598411868779</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1532914234747551</v>
+        <v>-0.1590401538774771</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0170768542656603</v>
+        <v>-0.0162242943246369</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1440883913765063</v>
+        <v>-0.1436679758290893</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2067655858611914</v>
+        <v>-0.2062049805493231</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2349604354223729</v>
+        <v>-0.2343143765947815</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.244631169394296</v>
+        <v>-0.2453151503219004</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2038476388391146</v>
+        <v>-0.2039614364362023</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1524436557901865</v>
+        <v>-0.1533614911261907</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.007828032100796634</v>
+        <v>0.00644398044671135</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1077786122332398</v>
+        <v>0.1054602344430222</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.0160177999049651</v>
+        <v>-0.01872548232577742</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01033699059468773</v>
+        <v>-0.01307618205879635</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.03587658454915044</v>
+        <v>-0.03920658595786364</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.02421167925289325</v>
+        <v>-0.02826650770485628</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.05508534874498849</v>
+        <v>-0.05970392146876691</v>
       </c>
     </row>
   </sheetData>
